--- a/Base_Donnees_Handball.xlsx
+++ b/Base_Donnees_Handball.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madje\Documents\FeuillesMatchs\Archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDA1F8C-B586-495C-80E6-A1470789DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2843F77D-001B-47A8-BA1F-9EB384BA4AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11831" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12662" uniqueCount="86">
   <si>
     <t>Journée</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>J16</t>
+  </si>
+  <si>
+    <t>BHB-BEL</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
   </si>
 </sst>
 </file>
@@ -631,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1889"/>
+  <dimension ref="A1:U2024"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
@@ -105046,6 +105055,7425 @@
         <v>6.25E-2</v>
       </c>
     </row>
+    <row r="1890" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1890" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1890" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1890" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1890" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1890">
+        <v>1</v>
+      </c>
+      <c r="G1890">
+        <v>1</v>
+      </c>
+      <c r="H1890" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1890">
+        <v>0</v>
+      </c>
+      <c r="K1890">
+        <v>0</v>
+      </c>
+      <c r="L1890">
+        <v>0</v>
+      </c>
+      <c r="M1890">
+        <v>0</v>
+      </c>
+      <c r="N1890">
+        <v>0</v>
+      </c>
+      <c r="O1890">
+        <v>0</v>
+      </c>
+      <c r="P1890">
+        <v>0</v>
+      </c>
+      <c r="Q1890">
+        <v>0</v>
+      </c>
+      <c r="S1890">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1891" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1891" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1891" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1891" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1891">
+        <v>2</v>
+      </c>
+      <c r="G1891">
+        <v>1</v>
+      </c>
+      <c r="H1891" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1891">
+        <v>0</v>
+      </c>
+      <c r="J1891">
+        <v>3</v>
+      </c>
+      <c r="K1891">
+        <v>0</v>
+      </c>
+      <c r="L1891">
+        <v>0</v>
+      </c>
+      <c r="M1891">
+        <v>0</v>
+      </c>
+      <c r="N1891">
+        <v>0</v>
+      </c>
+      <c r="O1891">
+        <v>0</v>
+      </c>
+      <c r="P1891">
+        <v>0</v>
+      </c>
+      <c r="Q1891">
+        <v>0</v>
+      </c>
+      <c r="S1891">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1892" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1892" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1892" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1892" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1892">
+        <v>3</v>
+      </c>
+      <c r="G1892">
+        <v>2</v>
+      </c>
+      <c r="H1892" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1892">
+        <v>0</v>
+      </c>
+      <c r="K1892">
+        <v>0</v>
+      </c>
+      <c r="L1892">
+        <v>0</v>
+      </c>
+      <c r="M1892">
+        <v>0</v>
+      </c>
+      <c r="N1892">
+        <v>0</v>
+      </c>
+      <c r="O1892">
+        <v>0</v>
+      </c>
+      <c r="P1892">
+        <v>0</v>
+      </c>
+      <c r="Q1892">
+        <v>0</v>
+      </c>
+      <c r="S1892">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1893" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1893" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1893" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1893" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1893">
+        <v>4</v>
+      </c>
+      <c r="G1893">
+        <v>3</v>
+      </c>
+      <c r="H1893" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1893">
+        <v>1</v>
+      </c>
+      <c r="J1893">
+        <v>3</v>
+      </c>
+      <c r="K1893">
+        <v>1</v>
+      </c>
+      <c r="L1893">
+        <v>0</v>
+      </c>
+      <c r="M1893">
+        <v>1</v>
+      </c>
+      <c r="N1893">
+        <v>0.5</v>
+      </c>
+      <c r="O1893">
+        <v>0</v>
+      </c>
+      <c r="P1893">
+        <v>0.25</v>
+      </c>
+      <c r="Q1893">
+        <v>0</v>
+      </c>
+      <c r="S1893">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1894" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1894" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1894" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1894" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1894">
+        <v>5</v>
+      </c>
+      <c r="G1894">
+        <v>4</v>
+      </c>
+      <c r="H1894" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1894">
+        <v>1</v>
+      </c>
+      <c r="K1894">
+        <v>1</v>
+      </c>
+      <c r="L1894">
+        <v>1</v>
+      </c>
+      <c r="M1894">
+        <v>0</v>
+      </c>
+      <c r="N1894">
+        <v>0.5</v>
+      </c>
+      <c r="O1894">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P1894">
+        <v>0.25</v>
+      </c>
+      <c r="Q1894">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S1894">
+        <v>0.1388888888888889</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1895" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1895" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1895" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1895" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1895">
+        <v>6</v>
+      </c>
+      <c r="G1895">
+        <v>4</v>
+      </c>
+      <c r="H1895" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1895">
+        <v>1</v>
+      </c>
+      <c r="J1895">
+        <v>8</v>
+      </c>
+      <c r="K1895">
+        <v>2</v>
+      </c>
+      <c r="L1895">
+        <v>1</v>
+      </c>
+      <c r="M1895">
+        <v>1</v>
+      </c>
+      <c r="N1895">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O1895">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P1895">
+        <v>0.38888888888888878</v>
+      </c>
+      <c r="Q1895">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S1895">
+        <v>0.27777777777777768</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1896" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1896" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1896" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1896" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1896">
+        <v>7</v>
+      </c>
+      <c r="G1896">
+        <v>5</v>
+      </c>
+      <c r="H1896" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1896">
+        <v>1</v>
+      </c>
+      <c r="K1896">
+        <v>2</v>
+      </c>
+      <c r="L1896">
+        <v>2</v>
+      </c>
+      <c r="M1896">
+        <v>0</v>
+      </c>
+      <c r="N1896">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O1896">
+        <v>0.5</v>
+      </c>
+      <c r="P1896">
+        <v>0.38888888888888878</v>
+      </c>
+      <c r="Q1896">
+        <v>0.20833333333333329</v>
+      </c>
+      <c r="S1896">
+        <v>0.1805555555555555</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1897" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1897" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1897" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1897" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1897">
+        <v>8</v>
+      </c>
+      <c r="G1897">
+        <v>5</v>
+      </c>
+      <c r="H1897" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1897">
+        <v>1</v>
+      </c>
+      <c r="J1897">
+        <v>9</v>
+      </c>
+      <c r="K1897">
+        <v>3</v>
+      </c>
+      <c r="L1897">
+        <v>2</v>
+      </c>
+      <c r="M1897">
+        <v>1</v>
+      </c>
+      <c r="N1897">
+        <v>0.75</v>
+      </c>
+      <c r="O1897">
+        <v>0.5</v>
+      </c>
+      <c r="P1897">
+        <v>0.47916666666666657</v>
+      </c>
+      <c r="Q1897">
+        <v>0.20833333333333329</v>
+      </c>
+      <c r="S1897">
+        <v>0.27083333333333331</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1898" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1898" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1898" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1898" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1898">
+        <v>9</v>
+      </c>
+      <c r="G1898">
+        <v>6</v>
+      </c>
+      <c r="H1898" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1898">
+        <v>0</v>
+      </c>
+      <c r="K1898">
+        <v>3</v>
+      </c>
+      <c r="L1898">
+        <v>2</v>
+      </c>
+      <c r="M1898">
+        <v>1</v>
+      </c>
+      <c r="N1898">
+        <v>0.75</v>
+      </c>
+      <c r="O1898">
+        <v>0.5</v>
+      </c>
+      <c r="P1898">
+        <v>0.47916666666666657</v>
+      </c>
+      <c r="Q1898">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="S1898">
+        <v>0.14583333333333329</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1899" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1899" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1899" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1899" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1899">
+        <v>10</v>
+      </c>
+      <c r="G1899">
+        <v>6</v>
+      </c>
+      <c r="H1899" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1899">
+        <v>1</v>
+      </c>
+      <c r="J1899">
+        <v>4</v>
+      </c>
+      <c r="K1899">
+        <v>4</v>
+      </c>
+      <c r="L1899">
+        <v>2</v>
+      </c>
+      <c r="M1899">
+        <v>2</v>
+      </c>
+      <c r="N1899">
+        <v>1</v>
+      </c>
+      <c r="O1899">
+        <v>0.5</v>
+      </c>
+      <c r="P1899">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="Q1899">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="S1899">
+        <v>0.39583333333333331</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1900" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1900" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1900" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1900" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1900">
+        <v>11</v>
+      </c>
+      <c r="G1900">
+        <v>7</v>
+      </c>
+      <c r="H1900" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1900">
+        <v>1</v>
+      </c>
+      <c r="K1900">
+        <v>4</v>
+      </c>
+      <c r="L1900">
+        <v>3</v>
+      </c>
+      <c r="M1900">
+        <v>1</v>
+      </c>
+      <c r="N1900">
+        <v>1</v>
+      </c>
+      <c r="O1900">
+        <v>0.75</v>
+      </c>
+      <c r="P1900">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="Q1900">
+        <v>0.52083333333333326</v>
+      </c>
+      <c r="S1900">
+        <v>0.2083333333333334</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1901" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1901" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1901" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1901" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1901">
+        <v>12</v>
+      </c>
+      <c r="G1901">
+        <v>7</v>
+      </c>
+      <c r="H1901" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1901">
+        <v>1</v>
+      </c>
+      <c r="J1901">
+        <v>24</v>
+      </c>
+      <c r="K1901">
+        <v>5</v>
+      </c>
+      <c r="L1901">
+        <v>3</v>
+      </c>
+      <c r="M1901">
+        <v>2</v>
+      </c>
+      <c r="N1901">
+        <v>1</v>
+      </c>
+      <c r="O1901">
+        <v>0.75</v>
+      </c>
+      <c r="P1901">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="Q1901">
+        <v>0.52083333333333326</v>
+      </c>
+      <c r="S1901">
+        <v>0.33333333333333343</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1902" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1902" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1902" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1902" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1902">
+        <v>13</v>
+      </c>
+      <c r="G1902">
+        <v>8</v>
+      </c>
+      <c r="H1902" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1902">
+        <v>1</v>
+      </c>
+      <c r="K1902">
+        <v>5</v>
+      </c>
+      <c r="L1902">
+        <v>4</v>
+      </c>
+      <c r="M1902">
+        <v>1</v>
+      </c>
+      <c r="N1902">
+        <v>1</v>
+      </c>
+      <c r="O1902">
+        <v>0.75</v>
+      </c>
+      <c r="P1902">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="Q1902">
+        <v>0.625</v>
+      </c>
+      <c r="S1902">
+        <v>0.2291666666666666</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1903" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1903" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1903" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1903" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1903">
+        <v>14</v>
+      </c>
+      <c r="G1903">
+        <v>8</v>
+      </c>
+      <c r="H1903" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1903">
+        <v>0</v>
+      </c>
+      <c r="J1903">
+        <v>9</v>
+      </c>
+      <c r="K1903">
+        <v>5</v>
+      </c>
+      <c r="L1903">
+        <v>4</v>
+      </c>
+      <c r="M1903">
+        <v>1</v>
+      </c>
+      <c r="N1903">
+        <v>0.75</v>
+      </c>
+      <c r="O1903">
+        <v>0.75</v>
+      </c>
+      <c r="P1903">
+        <v>0.875</v>
+      </c>
+      <c r="Q1903">
+        <v>0.625</v>
+      </c>
+      <c r="S1903">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1904" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1904" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1904" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1904" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1904">
+        <v>15</v>
+      </c>
+      <c r="G1904">
+        <v>8</v>
+      </c>
+      <c r="H1904" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1904">
+        <v>1</v>
+      </c>
+      <c r="K1904">
+        <v>5</v>
+      </c>
+      <c r="L1904">
+        <v>5</v>
+      </c>
+      <c r="M1904">
+        <v>0</v>
+      </c>
+      <c r="N1904">
+        <v>0.75</v>
+      </c>
+      <c r="O1904">
+        <v>0.75</v>
+      </c>
+      <c r="P1904">
+        <v>0.875</v>
+      </c>
+      <c r="Q1904">
+        <v>0.6875</v>
+      </c>
+      <c r="S1904">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1905" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1905" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1905" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1905" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1905">
+        <v>16</v>
+      </c>
+      <c r="G1905">
+        <v>9</v>
+      </c>
+      <c r="H1905" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1905">
+        <v>1</v>
+      </c>
+      <c r="J1905">
+        <v>24</v>
+      </c>
+      <c r="K1905">
+        <v>6</v>
+      </c>
+      <c r="L1905">
+        <v>5</v>
+      </c>
+      <c r="M1905">
+        <v>1</v>
+      </c>
+      <c r="N1905">
+        <v>0.75</v>
+      </c>
+      <c r="O1905">
+        <v>0.75</v>
+      </c>
+      <c r="P1905">
+        <v>0.875</v>
+      </c>
+      <c r="Q1905">
+        <v>0.6875</v>
+      </c>
+      <c r="S1905">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1906" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1906" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1906" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1906" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1906">
+        <v>17</v>
+      </c>
+      <c r="G1906">
+        <v>10</v>
+      </c>
+      <c r="H1906" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1906">
+        <v>1</v>
+      </c>
+      <c r="K1906">
+        <v>6</v>
+      </c>
+      <c r="L1906">
+        <v>6</v>
+      </c>
+      <c r="M1906">
+        <v>0</v>
+      </c>
+      <c r="N1906">
+        <v>0.75</v>
+      </c>
+      <c r="O1906">
+        <v>1</v>
+      </c>
+      <c r="P1906">
+        <v>0.875</v>
+      </c>
+      <c r="Q1906">
+        <v>0.8125</v>
+      </c>
+      <c r="S1906">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1907" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1907" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1907" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1907" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1907">
+        <v>18</v>
+      </c>
+      <c r="G1907">
+        <v>10</v>
+      </c>
+      <c r="H1907" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1907">
+        <v>1</v>
+      </c>
+      <c r="J1907">
+        <v>8</v>
+      </c>
+      <c r="K1907">
+        <v>7</v>
+      </c>
+      <c r="L1907">
+        <v>6</v>
+      </c>
+      <c r="M1907">
+        <v>1</v>
+      </c>
+      <c r="N1907">
+        <v>0.75</v>
+      </c>
+      <c r="O1907">
+        <v>1</v>
+      </c>
+      <c r="P1907">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1907">
+        <v>0.8125</v>
+      </c>
+      <c r="S1907">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1908" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1908" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1908" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1908" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1908">
+        <v>19</v>
+      </c>
+      <c r="G1908">
+        <v>10</v>
+      </c>
+      <c r="H1908" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1908">
+        <v>1</v>
+      </c>
+      <c r="K1908">
+        <v>7</v>
+      </c>
+      <c r="L1908">
+        <v>7</v>
+      </c>
+      <c r="M1908">
+        <v>0</v>
+      </c>
+      <c r="N1908">
+        <v>0.75</v>
+      </c>
+      <c r="O1908">
+        <v>1</v>
+      </c>
+      <c r="P1908">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1908">
+        <v>0.875</v>
+      </c>
+      <c r="S1908">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1909" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1909" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1909" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1909" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1909">
+        <v>20</v>
+      </c>
+      <c r="G1909">
+        <v>10</v>
+      </c>
+      <c r="H1909" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1909">
+        <v>0</v>
+      </c>
+      <c r="J1909">
+        <v>0</v>
+      </c>
+      <c r="K1909">
+        <v>7</v>
+      </c>
+      <c r="L1909">
+        <v>7</v>
+      </c>
+      <c r="M1909">
+        <v>0</v>
+      </c>
+      <c r="N1909">
+        <v>0.5</v>
+      </c>
+      <c r="O1909">
+        <v>1</v>
+      </c>
+      <c r="P1909">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1909">
+        <v>0.875</v>
+      </c>
+      <c r="S1909">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1910" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1910" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1910" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1910" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1910">
+        <v>21</v>
+      </c>
+      <c r="G1910">
+        <v>10</v>
+      </c>
+      <c r="H1910" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1910">
+        <v>0</v>
+      </c>
+      <c r="K1910">
+        <v>7</v>
+      </c>
+      <c r="L1910">
+        <v>7</v>
+      </c>
+      <c r="M1910">
+        <v>0</v>
+      </c>
+      <c r="N1910">
+        <v>0.5</v>
+      </c>
+      <c r="O1910">
+        <v>0.75</v>
+      </c>
+      <c r="P1910">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1910">
+        <v>0.875</v>
+      </c>
+      <c r="S1910">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1911" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1911" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1911" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1911" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1911">
+        <v>22</v>
+      </c>
+      <c r="G1911">
+        <v>11</v>
+      </c>
+      <c r="H1911" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1911">
+        <v>1</v>
+      </c>
+      <c r="J1911">
+        <v>8</v>
+      </c>
+      <c r="K1911">
+        <v>8</v>
+      </c>
+      <c r="L1911">
+        <v>7</v>
+      </c>
+      <c r="M1911">
+        <v>1</v>
+      </c>
+      <c r="N1911">
+        <v>0.75</v>
+      </c>
+      <c r="O1911">
+        <v>0.75</v>
+      </c>
+      <c r="P1911">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1911">
+        <v>0.875</v>
+      </c>
+      <c r="S1911">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1912" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1912" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1912" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1912" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1912">
+        <v>23</v>
+      </c>
+      <c r="G1912">
+        <v>11</v>
+      </c>
+      <c r="H1912" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1912">
+        <v>1</v>
+      </c>
+      <c r="K1912">
+        <v>8</v>
+      </c>
+      <c r="L1912">
+        <v>8</v>
+      </c>
+      <c r="M1912">
+        <v>0</v>
+      </c>
+      <c r="N1912">
+        <v>0.75</v>
+      </c>
+      <c r="O1912">
+        <v>0.75</v>
+      </c>
+      <c r="P1912">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1912">
+        <v>0.875</v>
+      </c>
+      <c r="S1912">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1913" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1913" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1913" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1913" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1913">
+        <v>24</v>
+      </c>
+      <c r="G1913">
+        <v>12</v>
+      </c>
+      <c r="H1913" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1913">
+        <v>1</v>
+      </c>
+      <c r="J1913">
+        <v>24</v>
+      </c>
+      <c r="K1913">
+        <v>9</v>
+      </c>
+      <c r="L1913">
+        <v>8</v>
+      </c>
+      <c r="M1913">
+        <v>1</v>
+      </c>
+      <c r="N1913">
+        <v>0.75</v>
+      </c>
+      <c r="O1913">
+        <v>0.75</v>
+      </c>
+      <c r="P1913">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1913">
+        <v>0.875</v>
+      </c>
+      <c r="S1913">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1914" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1914" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1914" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1914" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1914">
+        <v>25</v>
+      </c>
+      <c r="G1914">
+        <v>13</v>
+      </c>
+      <c r="H1914" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1914">
+        <v>0</v>
+      </c>
+      <c r="K1914">
+        <v>9</v>
+      </c>
+      <c r="L1914">
+        <v>8</v>
+      </c>
+      <c r="M1914">
+        <v>1</v>
+      </c>
+      <c r="N1914">
+        <v>0.75</v>
+      </c>
+      <c r="O1914">
+        <v>0.5</v>
+      </c>
+      <c r="P1914">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1914">
+        <v>0.75</v>
+      </c>
+      <c r="S1914">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1915" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1915" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1915" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1915" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1915">
+        <v>26</v>
+      </c>
+      <c r="G1915">
+        <v>14</v>
+      </c>
+      <c r="H1915" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1915">
+        <v>1</v>
+      </c>
+      <c r="J1915">
+        <v>2</v>
+      </c>
+      <c r="K1915">
+        <v>10</v>
+      </c>
+      <c r="L1915">
+        <v>8</v>
+      </c>
+      <c r="M1915">
+        <v>2</v>
+      </c>
+      <c r="N1915">
+        <v>0.75</v>
+      </c>
+      <c r="O1915">
+        <v>0.5</v>
+      </c>
+      <c r="P1915">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1915">
+        <v>0.75</v>
+      </c>
+      <c r="S1915">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1916" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1916" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1916" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1916" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1916">
+        <v>27</v>
+      </c>
+      <c r="G1916">
+        <v>14</v>
+      </c>
+      <c r="H1916" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1916">
+        <v>1</v>
+      </c>
+      <c r="K1916">
+        <v>10</v>
+      </c>
+      <c r="L1916">
+        <v>9</v>
+      </c>
+      <c r="M1916">
+        <v>1</v>
+      </c>
+      <c r="N1916">
+        <v>0.75</v>
+      </c>
+      <c r="O1916">
+        <v>0.5</v>
+      </c>
+      <c r="P1916">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1916">
+        <v>0.625</v>
+      </c>
+      <c r="S1916">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1917" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1917" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1917" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1917" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1917">
+        <v>28</v>
+      </c>
+      <c r="G1917">
+        <v>14</v>
+      </c>
+      <c r="H1917" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1917">
+        <v>1</v>
+      </c>
+      <c r="J1917">
+        <v>4</v>
+      </c>
+      <c r="K1917">
+        <v>11</v>
+      </c>
+      <c r="L1917">
+        <v>9</v>
+      </c>
+      <c r="M1917">
+        <v>2</v>
+      </c>
+      <c r="N1917">
+        <v>1</v>
+      </c>
+      <c r="O1917">
+        <v>0.5</v>
+      </c>
+      <c r="P1917">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1917">
+        <v>0.625</v>
+      </c>
+      <c r="S1917">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1918" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1918" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1918" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1918" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1918">
+        <v>29</v>
+      </c>
+      <c r="G1918">
+        <v>15</v>
+      </c>
+      <c r="H1918" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1918">
+        <v>1</v>
+      </c>
+      <c r="K1918">
+        <v>11</v>
+      </c>
+      <c r="L1918">
+        <v>10</v>
+      </c>
+      <c r="M1918">
+        <v>1</v>
+      </c>
+      <c r="N1918">
+        <v>1</v>
+      </c>
+      <c r="O1918">
+        <v>0.75</v>
+      </c>
+      <c r="P1918">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1918">
+        <v>0.625</v>
+      </c>
+      <c r="S1918">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1919" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1919" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1919" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1919" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1919">
+        <v>30</v>
+      </c>
+      <c r="G1919">
+        <v>15</v>
+      </c>
+      <c r="H1919" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1919">
+        <v>0</v>
+      </c>
+      <c r="J1919">
+        <v>9</v>
+      </c>
+      <c r="K1919">
+        <v>11</v>
+      </c>
+      <c r="L1919">
+        <v>10</v>
+      </c>
+      <c r="M1919">
+        <v>1</v>
+      </c>
+      <c r="N1919">
+        <v>0.75</v>
+      </c>
+      <c r="O1919">
+        <v>0.75</v>
+      </c>
+      <c r="P1919">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1919">
+        <v>0.625</v>
+      </c>
+      <c r="S1919">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1920" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1920" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1920" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1920" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1920">
+        <v>31</v>
+      </c>
+      <c r="G1920">
+        <v>16</v>
+      </c>
+      <c r="H1920" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1920">
+        <v>0</v>
+      </c>
+      <c r="K1920">
+        <v>11</v>
+      </c>
+      <c r="L1920">
+        <v>10</v>
+      </c>
+      <c r="M1920">
+        <v>1</v>
+      </c>
+      <c r="N1920">
+        <v>0.75</v>
+      </c>
+      <c r="O1920">
+        <v>0.5</v>
+      </c>
+      <c r="P1920">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1920">
+        <v>0.5625</v>
+      </c>
+      <c r="S1920">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1921" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1921" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1921" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1921" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1921">
+        <v>32</v>
+      </c>
+      <c r="G1921">
+        <v>16</v>
+      </c>
+      <c r="H1921" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1921">
+        <v>0</v>
+      </c>
+      <c r="J1921">
+        <v>0</v>
+      </c>
+      <c r="K1921">
+        <v>11</v>
+      </c>
+      <c r="L1921">
+        <v>10</v>
+      </c>
+      <c r="M1921">
+        <v>1</v>
+      </c>
+      <c r="N1921">
+        <v>0.5</v>
+      </c>
+      <c r="O1921">
+        <v>0.5</v>
+      </c>
+      <c r="P1921">
+        <v>0.75</v>
+      </c>
+      <c r="Q1921">
+        <v>0.5625</v>
+      </c>
+      <c r="R1921" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1921">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1922" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1922" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1922" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1922" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1922">
+        <v>33</v>
+      </c>
+      <c r="G1922">
+        <v>17</v>
+      </c>
+      <c r="H1922" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1922">
+        <v>1</v>
+      </c>
+      <c r="K1922">
+        <v>11</v>
+      </c>
+      <c r="L1922">
+        <v>11</v>
+      </c>
+      <c r="M1922">
+        <v>0</v>
+      </c>
+      <c r="N1922">
+        <v>0.5</v>
+      </c>
+      <c r="O1922">
+        <v>0.75</v>
+      </c>
+      <c r="P1922">
+        <v>0.75</v>
+      </c>
+      <c r="Q1922">
+        <v>0.625</v>
+      </c>
+      <c r="S1922">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1923" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1923" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1923" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1923" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1923">
+        <v>34</v>
+      </c>
+      <c r="G1923">
+        <v>17</v>
+      </c>
+      <c r="H1923" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1923">
+        <v>0</v>
+      </c>
+      <c r="J1923">
+        <v>25</v>
+      </c>
+      <c r="K1923">
+        <v>11</v>
+      </c>
+      <c r="L1923">
+        <v>11</v>
+      </c>
+      <c r="M1923">
+        <v>0</v>
+      </c>
+      <c r="N1923">
+        <v>0.25</v>
+      </c>
+      <c r="O1923">
+        <v>0.75</v>
+      </c>
+      <c r="P1923">
+        <v>0.625</v>
+      </c>
+      <c r="Q1923">
+        <v>0.625</v>
+      </c>
+      <c r="S1923">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1924" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1924" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1924" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1924" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1924">
+        <v>35</v>
+      </c>
+      <c r="G1924">
+        <v>18</v>
+      </c>
+      <c r="H1924" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1924">
+        <v>0</v>
+      </c>
+      <c r="K1924">
+        <v>11</v>
+      </c>
+      <c r="L1924">
+        <v>11</v>
+      </c>
+      <c r="M1924">
+        <v>0</v>
+      </c>
+      <c r="N1924">
+        <v>0.25</v>
+      </c>
+      <c r="O1924">
+        <v>0.5</v>
+      </c>
+      <c r="P1924">
+        <v>0.625</v>
+      </c>
+      <c r="Q1924">
+        <v>0.625</v>
+      </c>
+      <c r="S1924">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1925" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1925" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1925" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1925" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1925">
+        <v>36</v>
+      </c>
+      <c r="G1925">
+        <v>18</v>
+      </c>
+      <c r="H1925" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1925">
+        <v>0</v>
+      </c>
+      <c r="J1925">
+        <v>0</v>
+      </c>
+      <c r="K1925">
+        <v>11</v>
+      </c>
+      <c r="L1925">
+        <v>11</v>
+      </c>
+      <c r="M1925">
+        <v>0</v>
+      </c>
+      <c r="N1925">
+        <v>0</v>
+      </c>
+      <c r="O1925">
+        <v>0.5</v>
+      </c>
+      <c r="P1925">
+        <v>0.375</v>
+      </c>
+      <c r="Q1925">
+        <v>0.625</v>
+      </c>
+      <c r="S1925">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1926" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1926" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1926" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1926" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1926">
+        <v>37</v>
+      </c>
+      <c r="G1926">
+        <v>18</v>
+      </c>
+      <c r="H1926" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1926">
+        <v>1</v>
+      </c>
+      <c r="K1926">
+        <v>11</v>
+      </c>
+      <c r="L1926">
+        <v>12</v>
+      </c>
+      <c r="M1926">
+        <v>-1</v>
+      </c>
+      <c r="N1926">
+        <v>0</v>
+      </c>
+      <c r="O1926">
+        <v>0.5</v>
+      </c>
+      <c r="P1926">
+        <v>0.375</v>
+      </c>
+      <c r="Q1926">
+        <v>0.5625</v>
+      </c>
+      <c r="S1926">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1927" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1927" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1927" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1927" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1927">
+        <v>38</v>
+      </c>
+      <c r="G1927">
+        <v>18</v>
+      </c>
+      <c r="H1927" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1927">
+        <v>1</v>
+      </c>
+      <c r="J1927">
+        <v>8</v>
+      </c>
+      <c r="K1927">
+        <v>12</v>
+      </c>
+      <c r="L1927">
+        <v>12</v>
+      </c>
+      <c r="M1927">
+        <v>0</v>
+      </c>
+      <c r="N1927">
+        <v>0.25</v>
+      </c>
+      <c r="O1927">
+        <v>0.5</v>
+      </c>
+      <c r="P1927">
+        <v>0.25</v>
+      </c>
+      <c r="Q1927">
+        <v>0.5625</v>
+      </c>
+      <c r="S1927">
+        <v>-0.3125</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1928" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1928" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1928" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1928" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1928">
+        <v>39</v>
+      </c>
+      <c r="G1928">
+        <v>19</v>
+      </c>
+      <c r="H1928" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1928">
+        <v>1</v>
+      </c>
+      <c r="K1928">
+        <v>12</v>
+      </c>
+      <c r="L1928">
+        <v>13</v>
+      </c>
+      <c r="M1928">
+        <v>-1</v>
+      </c>
+      <c r="N1928">
+        <v>0.25</v>
+      </c>
+      <c r="O1928">
+        <v>0.75</v>
+      </c>
+      <c r="P1928">
+        <v>0.25</v>
+      </c>
+      <c r="Q1928">
+        <v>0.625</v>
+      </c>
+      <c r="S1928">
+        <v>-0.375</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1929" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1929" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1929" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1929" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1929">
+        <v>40</v>
+      </c>
+      <c r="G1929">
+        <v>19</v>
+      </c>
+      <c r="H1929" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1929">
+        <v>0</v>
+      </c>
+      <c r="J1929">
+        <v>0</v>
+      </c>
+      <c r="K1929">
+        <v>12</v>
+      </c>
+      <c r="L1929">
+        <v>13</v>
+      </c>
+      <c r="M1929">
+        <v>-1</v>
+      </c>
+      <c r="N1929">
+        <v>0.25</v>
+      </c>
+      <c r="O1929">
+        <v>0.75</v>
+      </c>
+      <c r="P1929">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1929">
+        <v>0.625</v>
+      </c>
+      <c r="S1929">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1930" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1930" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1930" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1930" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1930">
+        <v>41</v>
+      </c>
+      <c r="G1930">
+        <v>19</v>
+      </c>
+      <c r="H1930" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1930">
+        <v>1</v>
+      </c>
+      <c r="K1930">
+        <v>12</v>
+      </c>
+      <c r="L1930">
+        <v>14</v>
+      </c>
+      <c r="M1930">
+        <v>-2</v>
+      </c>
+      <c r="N1930">
+        <v>0.25</v>
+      </c>
+      <c r="O1930">
+        <v>0.75</v>
+      </c>
+      <c r="P1930">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1930">
+        <v>0.625</v>
+      </c>
+      <c r="R1930" t="s">
+        <v>42</v>
+      </c>
+      <c r="S1930">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1931" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1931" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1931" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1931" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1931">
+        <v>42</v>
+      </c>
+      <c r="G1931">
+        <v>20</v>
+      </c>
+      <c r="H1931" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1931">
+        <v>0</v>
+      </c>
+      <c r="J1931">
+        <v>2</v>
+      </c>
+      <c r="K1931">
+        <v>12</v>
+      </c>
+      <c r="L1931">
+        <v>14</v>
+      </c>
+      <c r="M1931">
+        <v>-2</v>
+      </c>
+      <c r="N1931">
+        <v>0.25</v>
+      </c>
+      <c r="O1931">
+        <v>0.75</v>
+      </c>
+      <c r="P1931">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1931">
+        <v>0.625</v>
+      </c>
+      <c r="S1931">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1932" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1932" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1932" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1932" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1932">
+        <v>43</v>
+      </c>
+      <c r="G1932">
+        <v>20</v>
+      </c>
+      <c r="H1932" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1932">
+        <v>1</v>
+      </c>
+      <c r="K1932">
+        <v>12</v>
+      </c>
+      <c r="L1932">
+        <v>15</v>
+      </c>
+      <c r="M1932">
+        <v>-3</v>
+      </c>
+      <c r="N1932">
+        <v>0.25</v>
+      </c>
+      <c r="O1932">
+        <v>1</v>
+      </c>
+      <c r="P1932">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1932">
+        <v>0.75</v>
+      </c>
+      <c r="S1932">
+        <v>-0.5625</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1933" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1933" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1933" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1933" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1933">
+        <v>44</v>
+      </c>
+      <c r="G1933">
+        <v>21</v>
+      </c>
+      <c r="H1933" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1933">
+        <v>0</v>
+      </c>
+      <c r="J1933">
+        <v>3</v>
+      </c>
+      <c r="K1933">
+        <v>12</v>
+      </c>
+      <c r="L1933">
+        <v>15</v>
+      </c>
+      <c r="M1933">
+        <v>-3</v>
+      </c>
+      <c r="N1933">
+        <v>0.25</v>
+      </c>
+      <c r="O1933">
+        <v>1</v>
+      </c>
+      <c r="P1933">
+        <v>0.25</v>
+      </c>
+      <c r="Q1933">
+        <v>0.75</v>
+      </c>
+      <c r="S1933">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1934" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1934" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1934" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1934" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1934">
+        <v>45</v>
+      </c>
+      <c r="G1934">
+        <v>21</v>
+      </c>
+      <c r="H1934" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1934">
+        <v>0</v>
+      </c>
+      <c r="K1934">
+        <v>12</v>
+      </c>
+      <c r="L1934">
+        <v>15</v>
+      </c>
+      <c r="M1934">
+        <v>-3</v>
+      </c>
+      <c r="N1934">
+        <v>0.25</v>
+      </c>
+      <c r="O1934">
+        <v>0.75</v>
+      </c>
+      <c r="P1934">
+        <v>0.25</v>
+      </c>
+      <c r="Q1934">
+        <v>0.8125</v>
+      </c>
+      <c r="S1934">
+        <v>-0.5625</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1935" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1935" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1935" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1935" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1935">
+        <v>46</v>
+      </c>
+      <c r="G1935">
+        <v>22</v>
+      </c>
+      <c r="H1935" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1935">
+        <v>0</v>
+      </c>
+      <c r="J1935">
+        <v>0</v>
+      </c>
+      <c r="K1935">
+        <v>12</v>
+      </c>
+      <c r="L1935">
+        <v>15</v>
+      </c>
+      <c r="M1935">
+        <v>-3</v>
+      </c>
+      <c r="N1935">
+        <v>0</v>
+      </c>
+      <c r="O1935">
+        <v>0.75</v>
+      </c>
+      <c r="P1935">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1935">
+        <v>0.8125</v>
+      </c>
+      <c r="S1935">
+        <v>-0.625</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1936" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1936" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1936" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1936" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1936">
+        <v>47</v>
+      </c>
+      <c r="G1936">
+        <v>22</v>
+      </c>
+      <c r="H1936" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1936">
+        <v>0</v>
+      </c>
+      <c r="K1936">
+        <v>12</v>
+      </c>
+      <c r="L1936">
+        <v>15</v>
+      </c>
+      <c r="M1936">
+        <v>-3</v>
+      </c>
+      <c r="N1936">
+        <v>0</v>
+      </c>
+      <c r="O1936">
+        <v>0.5</v>
+      </c>
+      <c r="P1936">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1936">
+        <v>0.75</v>
+      </c>
+      <c r="S1936">
+        <v>-0.5625</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1937" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1937" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1937" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1937" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1937">
+        <v>48</v>
+      </c>
+      <c r="G1937">
+        <v>22</v>
+      </c>
+      <c r="H1937" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1937">
+        <v>1</v>
+      </c>
+      <c r="J1937">
+        <v>2</v>
+      </c>
+      <c r="K1937">
+        <v>13</v>
+      </c>
+      <c r="L1937">
+        <v>15</v>
+      </c>
+      <c r="M1937">
+        <v>-2</v>
+      </c>
+      <c r="N1937">
+        <v>0.25</v>
+      </c>
+      <c r="O1937">
+        <v>0.5</v>
+      </c>
+      <c r="P1937">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1937">
+        <v>0.75</v>
+      </c>
+      <c r="S1937">
+        <v>-0.5625</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1938" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1938" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1938" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1938" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1938">
+        <v>49</v>
+      </c>
+      <c r="G1938">
+        <v>23</v>
+      </c>
+      <c r="H1938" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1938">
+        <v>0</v>
+      </c>
+      <c r="K1938">
+        <v>13</v>
+      </c>
+      <c r="L1938">
+        <v>15</v>
+      </c>
+      <c r="M1938">
+        <v>-2</v>
+      </c>
+      <c r="N1938">
+        <v>0.25</v>
+      </c>
+      <c r="O1938">
+        <v>0.25</v>
+      </c>
+      <c r="P1938">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1938">
+        <v>0.625</v>
+      </c>
+      <c r="S1938">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1939" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1939" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1939" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1939" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1939">
+        <v>50</v>
+      </c>
+      <c r="G1939">
+        <v>23</v>
+      </c>
+      <c r="H1939" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1939">
+        <v>0</v>
+      </c>
+      <c r="J1939">
+        <v>25</v>
+      </c>
+      <c r="K1939">
+        <v>13</v>
+      </c>
+      <c r="L1939">
+        <v>15</v>
+      </c>
+      <c r="M1939">
+        <v>-2</v>
+      </c>
+      <c r="N1939">
+        <v>0.25</v>
+      </c>
+      <c r="O1939">
+        <v>0.25</v>
+      </c>
+      <c r="P1939">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1939">
+        <v>0.625</v>
+      </c>
+      <c r="S1939">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1940" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1940" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1940" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1940" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1940">
+        <v>51</v>
+      </c>
+      <c r="G1940">
+        <v>24</v>
+      </c>
+      <c r="H1940" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1940">
+        <v>1</v>
+      </c>
+      <c r="K1940">
+        <v>13</v>
+      </c>
+      <c r="L1940">
+        <v>16</v>
+      </c>
+      <c r="M1940">
+        <v>-3</v>
+      </c>
+      <c r="N1940">
+        <v>0.25</v>
+      </c>
+      <c r="O1940">
+        <v>0.25</v>
+      </c>
+      <c r="P1940">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1940">
+        <v>0.4375</v>
+      </c>
+      <c r="S1940">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1941" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1941" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1941" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1941" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1941">
+        <v>52</v>
+      </c>
+      <c r="G1941">
+        <v>24</v>
+      </c>
+      <c r="H1941" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1941">
+        <v>1</v>
+      </c>
+      <c r="J1941">
+        <v>4</v>
+      </c>
+      <c r="K1941">
+        <v>14</v>
+      </c>
+      <c r="L1941">
+        <v>16</v>
+      </c>
+      <c r="M1941">
+        <v>-2</v>
+      </c>
+      <c r="N1941">
+        <v>0.5</v>
+      </c>
+      <c r="O1941">
+        <v>0.25</v>
+      </c>
+      <c r="P1941">
+        <v>0.25</v>
+      </c>
+      <c r="Q1941">
+        <v>0.4375</v>
+      </c>
+      <c r="S1941">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1942" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1942" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1942" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1942" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1942">
+        <v>53</v>
+      </c>
+      <c r="G1942">
+        <v>25</v>
+      </c>
+      <c r="H1942" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1942">
+        <v>1</v>
+      </c>
+      <c r="K1942">
+        <v>14</v>
+      </c>
+      <c r="L1942">
+        <v>17</v>
+      </c>
+      <c r="M1942">
+        <v>-3</v>
+      </c>
+      <c r="N1942">
+        <v>0.5</v>
+      </c>
+      <c r="O1942">
+        <v>0.5</v>
+      </c>
+      <c r="P1942">
+        <v>0.25</v>
+      </c>
+      <c r="Q1942">
+        <v>0.375</v>
+      </c>
+      <c r="S1942">
+        <v>-0.125</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1943" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1943" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1943" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1943" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1943">
+        <v>54</v>
+      </c>
+      <c r="G1943">
+        <v>26</v>
+      </c>
+      <c r="H1943" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1943">
+        <v>0</v>
+      </c>
+      <c r="J1943">
+        <v>0</v>
+      </c>
+      <c r="K1943">
+        <v>14</v>
+      </c>
+      <c r="L1943">
+        <v>17</v>
+      </c>
+      <c r="M1943">
+        <v>-3</v>
+      </c>
+      <c r="N1943">
+        <v>0.5</v>
+      </c>
+      <c r="O1943">
+        <v>0.5</v>
+      </c>
+      <c r="P1943">
+        <v>0.375</v>
+      </c>
+      <c r="Q1943">
+        <v>0.375</v>
+      </c>
+      <c r="S1943">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1944" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1944" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1944" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1944" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1944">
+        <v>55</v>
+      </c>
+      <c r="G1944">
+        <v>26</v>
+      </c>
+      <c r="H1944" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1944">
+        <v>1</v>
+      </c>
+      <c r="K1944">
+        <v>14</v>
+      </c>
+      <c r="L1944">
+        <v>18</v>
+      </c>
+      <c r="M1944">
+        <v>-4</v>
+      </c>
+      <c r="N1944">
+        <v>0.5</v>
+      </c>
+      <c r="O1944">
+        <v>0.75</v>
+      </c>
+      <c r="P1944">
+        <v>0.375</v>
+      </c>
+      <c r="Q1944">
+        <v>0.4375</v>
+      </c>
+      <c r="S1944">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1945" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1945" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1945" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1945" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1945">
+        <v>56</v>
+      </c>
+      <c r="G1945">
+        <v>26</v>
+      </c>
+      <c r="H1945" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1945">
+        <v>1</v>
+      </c>
+      <c r="J1945">
+        <v>10</v>
+      </c>
+      <c r="K1945">
+        <v>15</v>
+      </c>
+      <c r="L1945">
+        <v>18</v>
+      </c>
+      <c r="M1945">
+        <v>-3</v>
+      </c>
+      <c r="N1945">
+        <v>0.5</v>
+      </c>
+      <c r="O1945">
+        <v>0.75</v>
+      </c>
+      <c r="P1945">
+        <v>0.4375</v>
+      </c>
+      <c r="Q1945">
+        <v>0.4375</v>
+      </c>
+      <c r="S1945">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1946" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1946" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1946" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1946" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1946">
+        <v>57</v>
+      </c>
+      <c r="G1946">
+        <v>26</v>
+      </c>
+      <c r="H1946" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1946">
+        <v>0</v>
+      </c>
+      <c r="K1946">
+        <v>15</v>
+      </c>
+      <c r="L1946">
+        <v>18</v>
+      </c>
+      <c r="M1946">
+        <v>-3</v>
+      </c>
+      <c r="N1946">
+        <v>0.5</v>
+      </c>
+      <c r="O1946">
+        <v>0.75</v>
+      </c>
+      <c r="P1946">
+        <v>0.4375</v>
+      </c>
+      <c r="Q1946">
+        <v>0.5625</v>
+      </c>
+      <c r="S1946">
+        <v>-0.125</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1947" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1947" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1947" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1947" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1947">
+        <v>58</v>
+      </c>
+      <c r="G1947">
+        <v>27</v>
+      </c>
+      <c r="H1947" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1947">
+        <v>1</v>
+      </c>
+      <c r="J1947">
+        <v>8</v>
+      </c>
+      <c r="K1947">
+        <v>16</v>
+      </c>
+      <c r="L1947">
+        <v>18</v>
+      </c>
+      <c r="M1947">
+        <v>-2</v>
+      </c>
+      <c r="N1947">
+        <v>0.75</v>
+      </c>
+      <c r="O1947">
+        <v>0.75</v>
+      </c>
+      <c r="P1947">
+        <v>0.5625</v>
+      </c>
+      <c r="Q1947">
+        <v>0.5625</v>
+      </c>
+      <c r="S1947">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1948" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1948" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1948" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1948" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1948">
+        <v>59</v>
+      </c>
+      <c r="G1948">
+        <v>27</v>
+      </c>
+      <c r="H1948" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1948">
+        <v>1</v>
+      </c>
+      <c r="K1948">
+        <v>16</v>
+      </c>
+      <c r="L1948">
+        <v>19</v>
+      </c>
+      <c r="M1948">
+        <v>-3</v>
+      </c>
+      <c r="N1948">
+        <v>0.75</v>
+      </c>
+      <c r="O1948">
+        <v>0.75</v>
+      </c>
+      <c r="P1948">
+        <v>0.5625</v>
+      </c>
+      <c r="Q1948">
+        <v>0.6875</v>
+      </c>
+      <c r="S1948">
+        <v>-0.125</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1949" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1949" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1949" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1949" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1949">
+        <v>60</v>
+      </c>
+      <c r="G1949">
+        <v>28</v>
+      </c>
+      <c r="H1949" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1949">
+        <v>0</v>
+      </c>
+      <c r="J1949">
+        <v>0</v>
+      </c>
+      <c r="K1949">
+        <v>16</v>
+      </c>
+      <c r="L1949">
+        <v>19</v>
+      </c>
+      <c r="M1949">
+        <v>-3</v>
+      </c>
+      <c r="N1949">
+        <v>0.5</v>
+      </c>
+      <c r="O1949">
+        <v>0.75</v>
+      </c>
+      <c r="P1949">
+        <v>0.5625</v>
+      </c>
+      <c r="Q1949">
+        <v>0.6875</v>
+      </c>
+      <c r="S1949">
+        <v>-0.125</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1950" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1950" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1950" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1950" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1950">
+        <v>61</v>
+      </c>
+      <c r="G1950">
+        <v>28</v>
+      </c>
+      <c r="H1950" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1950">
+        <v>0</v>
+      </c>
+      <c r="K1950">
+        <v>16</v>
+      </c>
+      <c r="L1950">
+        <v>19</v>
+      </c>
+      <c r="M1950">
+        <v>-3</v>
+      </c>
+      <c r="N1950">
+        <v>0.5</v>
+      </c>
+      <c r="O1950">
+        <v>0.5</v>
+      </c>
+      <c r="P1950">
+        <v>0.5625</v>
+      </c>
+      <c r="Q1950">
+        <v>0.6875</v>
+      </c>
+      <c r="S1950">
+        <v>-0.125</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1951" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1951" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1951" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1951" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1951">
+        <v>62</v>
+      </c>
+      <c r="G1951">
+        <v>28</v>
+      </c>
+      <c r="H1951" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1951">
+        <v>1</v>
+      </c>
+      <c r="J1951">
+        <v>10</v>
+      </c>
+      <c r="K1951">
+        <v>17</v>
+      </c>
+      <c r="L1951">
+        <v>19</v>
+      </c>
+      <c r="M1951">
+        <v>-2</v>
+      </c>
+      <c r="N1951">
+        <v>0.75</v>
+      </c>
+      <c r="O1951">
+        <v>0.5</v>
+      </c>
+      <c r="P1951">
+        <v>0.625</v>
+      </c>
+      <c r="Q1951">
+        <v>0.6875</v>
+      </c>
+      <c r="S1951">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1952" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1952" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1952" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1952" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1952">
+        <v>63</v>
+      </c>
+      <c r="G1952">
+        <v>29</v>
+      </c>
+      <c r="H1952" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1952">
+        <v>1</v>
+      </c>
+      <c r="K1952">
+        <v>17</v>
+      </c>
+      <c r="L1952">
+        <v>20</v>
+      </c>
+      <c r="M1952">
+        <v>-3</v>
+      </c>
+      <c r="N1952">
+        <v>0.75</v>
+      </c>
+      <c r="O1952">
+        <v>0.5</v>
+      </c>
+      <c r="P1952">
+        <v>0.625</v>
+      </c>
+      <c r="Q1952">
+        <v>0.625</v>
+      </c>
+      <c r="S1952">
+        <v>0</v>
+      </c>
+      <c r="U1952" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1953" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1953" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1953" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1953" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1953">
+        <v>64</v>
+      </c>
+      <c r="G1953">
+        <v>29</v>
+      </c>
+      <c r="H1953" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1953">
+        <v>1</v>
+      </c>
+      <c r="J1953">
+        <v>10</v>
+      </c>
+      <c r="K1953">
+        <v>18</v>
+      </c>
+      <c r="L1953">
+        <v>20</v>
+      </c>
+      <c r="M1953">
+        <v>-2</v>
+      </c>
+      <c r="N1953">
+        <v>0.75</v>
+      </c>
+      <c r="O1953">
+        <v>0.5</v>
+      </c>
+      <c r="P1953">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1953">
+        <v>0.625</v>
+      </c>
+      <c r="S1953">
+        <v>6.25E-2</v>
+      </c>
+      <c r="U1953" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1954" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1954" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1954" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1954" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1954">
+        <v>65</v>
+      </c>
+      <c r="G1954">
+        <v>30</v>
+      </c>
+      <c r="H1954" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1954">
+        <v>0</v>
+      </c>
+      <c r="K1954">
+        <v>18</v>
+      </c>
+      <c r="L1954">
+        <v>20</v>
+      </c>
+      <c r="M1954">
+        <v>-2</v>
+      </c>
+      <c r="N1954">
+        <v>0.75</v>
+      </c>
+      <c r="O1954">
+        <v>0.5</v>
+      </c>
+      <c r="P1954">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1954">
+        <v>0.5625</v>
+      </c>
+      <c r="S1954">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1955" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1955" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1955" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1955" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1955">
+        <v>66</v>
+      </c>
+      <c r="G1955">
+        <v>30</v>
+      </c>
+      <c r="H1955" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1955">
+        <v>1</v>
+      </c>
+      <c r="J1955">
+        <v>25</v>
+      </c>
+      <c r="K1955">
+        <v>19</v>
+      </c>
+      <c r="L1955">
+        <v>20</v>
+      </c>
+      <c r="M1955">
+        <v>-1</v>
+      </c>
+      <c r="N1955">
+        <v>0.75</v>
+      </c>
+      <c r="O1955">
+        <v>0.5</v>
+      </c>
+      <c r="P1955">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1955">
+        <v>0.5625</v>
+      </c>
+      <c r="S1955">
+        <v>0.125</v>
+      </c>
+      <c r="U1955" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1956" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1956" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1956" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1956" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1956">
+        <v>67</v>
+      </c>
+      <c r="G1956">
+        <v>30</v>
+      </c>
+      <c r="H1956" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1956">
+        <v>0</v>
+      </c>
+      <c r="K1956">
+        <v>19</v>
+      </c>
+      <c r="L1956">
+        <v>20</v>
+      </c>
+      <c r="M1956">
+        <v>-1</v>
+      </c>
+      <c r="N1956">
+        <v>0.75</v>
+      </c>
+      <c r="O1956">
+        <v>0.25</v>
+      </c>
+      <c r="P1956">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1956">
+        <v>0.4375</v>
+      </c>
+      <c r="S1956">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1957" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1957" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1957" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1957" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1957">
+        <v>68</v>
+      </c>
+      <c r="G1957">
+        <v>30</v>
+      </c>
+      <c r="H1957" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1957">
+        <v>1</v>
+      </c>
+      <c r="J1957">
+        <v>19</v>
+      </c>
+      <c r="K1957">
+        <v>20</v>
+      </c>
+      <c r="L1957">
+        <v>20</v>
+      </c>
+      <c r="M1957">
+        <v>0</v>
+      </c>
+      <c r="N1957">
+        <v>1</v>
+      </c>
+      <c r="O1957">
+        <v>0.25</v>
+      </c>
+      <c r="P1957">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1957">
+        <v>0.4375</v>
+      </c>
+      <c r="S1957">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1958" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1958" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1958" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1958" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1958">
+        <v>69</v>
+      </c>
+      <c r="G1958">
+        <v>31</v>
+      </c>
+      <c r="H1958" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1958">
+        <v>0</v>
+      </c>
+      <c r="K1958">
+        <v>20</v>
+      </c>
+      <c r="L1958">
+        <v>20</v>
+      </c>
+      <c r="M1958">
+        <v>0</v>
+      </c>
+      <c r="N1958">
+        <v>1</v>
+      </c>
+      <c r="O1958">
+        <v>0.25</v>
+      </c>
+      <c r="P1958">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1958">
+        <v>0.375</v>
+      </c>
+      <c r="S1958">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1959" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1959" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1959" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1959" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1959">
+        <v>70</v>
+      </c>
+      <c r="G1959">
+        <v>31</v>
+      </c>
+      <c r="H1959" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1959">
+        <v>0</v>
+      </c>
+      <c r="J1959">
+        <v>25</v>
+      </c>
+      <c r="K1959">
+        <v>20</v>
+      </c>
+      <c r="L1959">
+        <v>20</v>
+      </c>
+      <c r="M1959">
+        <v>0</v>
+      </c>
+      <c r="N1959">
+        <v>0.75</v>
+      </c>
+      <c r="O1959">
+        <v>0.25</v>
+      </c>
+      <c r="P1959">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1959">
+        <v>0.375</v>
+      </c>
+      <c r="S1959">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1960" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1960" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1960" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1960" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1960">
+        <v>71</v>
+      </c>
+      <c r="G1960">
+        <v>32</v>
+      </c>
+      <c r="H1960" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1960">
+        <v>1</v>
+      </c>
+      <c r="K1960">
+        <v>20</v>
+      </c>
+      <c r="L1960">
+        <v>21</v>
+      </c>
+      <c r="M1960">
+        <v>-1</v>
+      </c>
+      <c r="N1960">
+        <v>0.75</v>
+      </c>
+      <c r="O1960">
+        <v>0.25</v>
+      </c>
+      <c r="P1960">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1960">
+        <v>0.3125</v>
+      </c>
+      <c r="S1960">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1961" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1961" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1961" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1961" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1961">
+        <v>72</v>
+      </c>
+      <c r="G1961">
+        <v>32</v>
+      </c>
+      <c r="H1961" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1961">
+        <v>1</v>
+      </c>
+      <c r="J1961">
+        <v>2</v>
+      </c>
+      <c r="K1961">
+        <v>21</v>
+      </c>
+      <c r="L1961">
+        <v>21</v>
+      </c>
+      <c r="M1961">
+        <v>0</v>
+      </c>
+      <c r="N1961">
+        <v>0.75</v>
+      </c>
+      <c r="O1961">
+        <v>0.25</v>
+      </c>
+      <c r="P1961">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1961">
+        <v>0.3125</v>
+      </c>
+      <c r="S1961">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1962" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1962" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1962" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1962" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1962">
+        <v>73</v>
+      </c>
+      <c r="G1962">
+        <v>32</v>
+      </c>
+      <c r="H1962" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1962">
+        <v>0</v>
+      </c>
+      <c r="K1962">
+        <v>21</v>
+      </c>
+      <c r="L1962">
+        <v>21</v>
+      </c>
+      <c r="M1962">
+        <v>0</v>
+      </c>
+      <c r="N1962">
+        <v>0.75</v>
+      </c>
+      <c r="O1962">
+        <v>0.25</v>
+      </c>
+      <c r="P1962">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1962">
+        <v>0.25</v>
+      </c>
+      <c r="S1962">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1963" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1963" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1963" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1963" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1963">
+        <v>74</v>
+      </c>
+      <c r="G1963">
+        <v>33</v>
+      </c>
+      <c r="H1963" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1963">
+        <v>0</v>
+      </c>
+      <c r="J1963">
+        <v>2</v>
+      </c>
+      <c r="K1963">
+        <v>21</v>
+      </c>
+      <c r="L1963">
+        <v>21</v>
+      </c>
+      <c r="M1963">
+        <v>0</v>
+      </c>
+      <c r="N1963">
+        <v>0.5</v>
+      </c>
+      <c r="O1963">
+        <v>0.25</v>
+      </c>
+      <c r="P1963">
+        <v>0.75</v>
+      </c>
+      <c r="Q1963">
+        <v>0.25</v>
+      </c>
+      <c r="S1963">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1964" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1964" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1964" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1964" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1964">
+        <v>75</v>
+      </c>
+      <c r="G1964">
+        <v>33</v>
+      </c>
+      <c r="H1964" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1964">
+        <v>0</v>
+      </c>
+      <c r="K1964">
+        <v>21</v>
+      </c>
+      <c r="L1964">
+        <v>21</v>
+      </c>
+      <c r="M1964">
+        <v>0</v>
+      </c>
+      <c r="N1964">
+        <v>0.5</v>
+      </c>
+      <c r="O1964">
+        <v>0.25</v>
+      </c>
+      <c r="P1964">
+        <v>0.75</v>
+      </c>
+      <c r="Q1964">
+        <v>0.25</v>
+      </c>
+      <c r="S1964">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1965" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1965" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1965" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1965" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1965">
+        <v>76</v>
+      </c>
+      <c r="G1965">
+        <v>33</v>
+      </c>
+      <c r="H1965" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1965">
+        <v>1</v>
+      </c>
+      <c r="J1965">
+        <v>25</v>
+      </c>
+      <c r="K1965">
+        <v>22</v>
+      </c>
+      <c r="L1965">
+        <v>21</v>
+      </c>
+      <c r="M1965">
+        <v>1</v>
+      </c>
+      <c r="N1965">
+        <v>0.5</v>
+      </c>
+      <c r="O1965">
+        <v>0.25</v>
+      </c>
+      <c r="P1965">
+        <v>0.625</v>
+      </c>
+      <c r="Q1965">
+        <v>0.25</v>
+      </c>
+      <c r="S1965">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1966" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1966" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1966" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1966" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1966">
+        <v>77</v>
+      </c>
+      <c r="G1966">
+        <v>34</v>
+      </c>
+      <c r="H1966" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1966">
+        <v>1</v>
+      </c>
+      <c r="K1966">
+        <v>22</v>
+      </c>
+      <c r="L1966">
+        <v>22</v>
+      </c>
+      <c r="M1966">
+        <v>0</v>
+      </c>
+      <c r="N1966">
+        <v>0.5</v>
+      </c>
+      <c r="O1966">
+        <v>0.5</v>
+      </c>
+      <c r="P1966">
+        <v>0.625</v>
+      </c>
+      <c r="Q1966">
+        <v>0.3125</v>
+      </c>
+      <c r="S1966">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1967" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1967" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1967" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1967" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1967">
+        <v>78</v>
+      </c>
+      <c r="G1967">
+        <v>35</v>
+      </c>
+      <c r="H1967" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1967">
+        <v>1</v>
+      </c>
+      <c r="J1967">
+        <v>10</v>
+      </c>
+      <c r="K1967">
+        <v>23</v>
+      </c>
+      <c r="L1967">
+        <v>22</v>
+      </c>
+      <c r="M1967">
+        <v>1</v>
+      </c>
+      <c r="N1967">
+        <v>0.75</v>
+      </c>
+      <c r="O1967">
+        <v>0.5</v>
+      </c>
+      <c r="P1967">
+        <v>0.625</v>
+      </c>
+      <c r="Q1967">
+        <v>0.3125</v>
+      </c>
+      <c r="S1967">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1968" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1968" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1968" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1968" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1968">
+        <v>79</v>
+      </c>
+      <c r="G1968">
+        <v>35</v>
+      </c>
+      <c r="H1968" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1968">
+        <v>0</v>
+      </c>
+      <c r="K1968">
+        <v>23</v>
+      </c>
+      <c r="L1968">
+        <v>22</v>
+      </c>
+      <c r="M1968">
+        <v>1</v>
+      </c>
+      <c r="N1968">
+        <v>0.75</v>
+      </c>
+      <c r="O1968">
+        <v>0.25</v>
+      </c>
+      <c r="P1968">
+        <v>0.625</v>
+      </c>
+      <c r="Q1968">
+        <v>0.3125</v>
+      </c>
+      <c r="S1968">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1969" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1969" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1969" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1969" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1969">
+        <v>80</v>
+      </c>
+      <c r="G1969">
+        <v>35</v>
+      </c>
+      <c r="H1969" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1969">
+        <v>1</v>
+      </c>
+      <c r="J1969">
+        <v>25</v>
+      </c>
+      <c r="K1969">
+        <v>24</v>
+      </c>
+      <c r="L1969">
+        <v>22</v>
+      </c>
+      <c r="M1969">
+        <v>2</v>
+      </c>
+      <c r="N1969">
+        <v>0.75</v>
+      </c>
+      <c r="O1969">
+        <v>0.25</v>
+      </c>
+      <c r="P1969">
+        <v>0.625</v>
+      </c>
+      <c r="Q1969">
+        <v>0.3125</v>
+      </c>
+      <c r="S1969">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1970" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1970" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1970" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1970" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1970">
+        <v>81</v>
+      </c>
+      <c r="G1970">
+        <v>36</v>
+      </c>
+      <c r="H1970" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1970">
+        <v>1</v>
+      </c>
+      <c r="K1970">
+        <v>24</v>
+      </c>
+      <c r="L1970">
+        <v>23</v>
+      </c>
+      <c r="M1970">
+        <v>1</v>
+      </c>
+      <c r="N1970">
+        <v>0.75</v>
+      </c>
+      <c r="O1970">
+        <v>0.5</v>
+      </c>
+      <c r="P1970">
+        <v>0.625</v>
+      </c>
+      <c r="Q1970">
+        <v>0.375</v>
+      </c>
+      <c r="S1970">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1971" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1971" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1971" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1971" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1971">
+        <v>82</v>
+      </c>
+      <c r="G1971">
+        <v>37</v>
+      </c>
+      <c r="H1971" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1971">
+        <v>1</v>
+      </c>
+      <c r="J1971">
+        <v>2</v>
+      </c>
+      <c r="K1971">
+        <v>25</v>
+      </c>
+      <c r="L1971">
+        <v>23</v>
+      </c>
+      <c r="M1971">
+        <v>2</v>
+      </c>
+      <c r="N1971">
+        <v>1</v>
+      </c>
+      <c r="O1971">
+        <v>0.5</v>
+      </c>
+      <c r="P1971">
+        <v>0.75</v>
+      </c>
+      <c r="Q1971">
+        <v>0.375</v>
+      </c>
+      <c r="S1971">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1972" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1972" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1972" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1972" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1972">
+        <v>83</v>
+      </c>
+      <c r="G1972">
+        <v>37</v>
+      </c>
+      <c r="H1972" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1972">
+        <v>1</v>
+      </c>
+      <c r="K1972">
+        <v>25</v>
+      </c>
+      <c r="L1972">
+        <v>24</v>
+      </c>
+      <c r="M1972">
+        <v>1</v>
+      </c>
+      <c r="N1972">
+        <v>1</v>
+      </c>
+      <c r="O1972">
+        <v>0.75</v>
+      </c>
+      <c r="P1972">
+        <v>0.75</v>
+      </c>
+      <c r="Q1972">
+        <v>0.5</v>
+      </c>
+      <c r="S1972">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1973" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1973" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1973" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1973" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1973">
+        <v>84</v>
+      </c>
+      <c r="G1973">
+        <v>37</v>
+      </c>
+      <c r="H1973" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1973">
+        <v>1</v>
+      </c>
+      <c r="J1973">
+        <v>2</v>
+      </c>
+      <c r="K1973">
+        <v>26</v>
+      </c>
+      <c r="L1973">
+        <v>24</v>
+      </c>
+      <c r="M1973">
+        <v>2</v>
+      </c>
+      <c r="N1973">
+        <v>1</v>
+      </c>
+      <c r="O1973">
+        <v>0.75</v>
+      </c>
+      <c r="P1973">
+        <v>0.875</v>
+      </c>
+      <c r="Q1973">
+        <v>0.5</v>
+      </c>
+      <c r="S1973">
+        <v>0.375</v>
+      </c>
+      <c r="U1973" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1974" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1974" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1974" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1974" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1974">
+        <v>85</v>
+      </c>
+      <c r="G1974">
+        <v>38</v>
+      </c>
+      <c r="H1974" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1974">
+        <v>0</v>
+      </c>
+      <c r="K1974">
+        <v>26</v>
+      </c>
+      <c r="L1974">
+        <v>24</v>
+      </c>
+      <c r="M1974">
+        <v>2</v>
+      </c>
+      <c r="N1974">
+        <v>1</v>
+      </c>
+      <c r="O1974">
+        <v>0.5</v>
+      </c>
+      <c r="P1974">
+        <v>0.875</v>
+      </c>
+      <c r="Q1974">
+        <v>0.5</v>
+      </c>
+      <c r="S1974">
+        <v>0.375</v>
+      </c>
+      <c r="U1974" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1975" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1975" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1975" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1975" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1975">
+        <v>86</v>
+      </c>
+      <c r="G1975">
+        <v>38</v>
+      </c>
+      <c r="H1975" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1975">
+        <v>1</v>
+      </c>
+      <c r="J1975">
+        <v>24</v>
+      </c>
+      <c r="K1975">
+        <v>27</v>
+      </c>
+      <c r="L1975">
+        <v>24</v>
+      </c>
+      <c r="M1975">
+        <v>3</v>
+      </c>
+      <c r="N1975">
+        <v>1</v>
+      </c>
+      <c r="O1975">
+        <v>0.5</v>
+      </c>
+      <c r="P1975">
+        <v>0.9375</v>
+      </c>
+      <c r="Q1975">
+        <v>0.5</v>
+      </c>
+      <c r="S1975">
+        <v>0.4375</v>
+      </c>
+      <c r="U1975" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1976" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1976" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1976" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1976" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1976">
+        <v>87</v>
+      </c>
+      <c r="G1976">
+        <v>38</v>
+      </c>
+      <c r="H1976" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1976">
+        <v>1</v>
+      </c>
+      <c r="K1976">
+        <v>27</v>
+      </c>
+      <c r="L1976">
+        <v>25</v>
+      </c>
+      <c r="M1976">
+        <v>2</v>
+      </c>
+      <c r="N1976">
+        <v>1</v>
+      </c>
+      <c r="O1976">
+        <v>0.75</v>
+      </c>
+      <c r="P1976">
+        <v>0.9375</v>
+      </c>
+      <c r="Q1976">
+        <v>0.625</v>
+      </c>
+      <c r="S1976">
+        <v>0.3125</v>
+      </c>
+      <c r="U1976" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1977" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1977" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1977" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1977" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1977">
+        <v>88</v>
+      </c>
+      <c r="G1977">
+        <v>39</v>
+      </c>
+      <c r="H1977" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1977">
+        <v>1</v>
+      </c>
+      <c r="J1977">
+        <v>24</v>
+      </c>
+      <c r="K1977">
+        <v>28</v>
+      </c>
+      <c r="L1977">
+        <v>25</v>
+      </c>
+      <c r="M1977">
+        <v>3</v>
+      </c>
+      <c r="N1977">
+        <v>1</v>
+      </c>
+      <c r="O1977">
+        <v>0.75</v>
+      </c>
+      <c r="P1977">
+        <v>1</v>
+      </c>
+      <c r="Q1977">
+        <v>0.625</v>
+      </c>
+      <c r="S1977">
+        <v>0.375</v>
+      </c>
+      <c r="U1977" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1978" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1978" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1978" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1978" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1978">
+        <v>89</v>
+      </c>
+      <c r="G1978">
+        <v>39</v>
+      </c>
+      <c r="H1978" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1978">
+        <v>0</v>
+      </c>
+      <c r="K1978">
+        <v>28</v>
+      </c>
+      <c r="L1978">
+        <v>25</v>
+      </c>
+      <c r="M1978">
+        <v>3</v>
+      </c>
+      <c r="N1978">
+        <v>1</v>
+      </c>
+      <c r="O1978">
+        <v>0.5</v>
+      </c>
+      <c r="P1978">
+        <v>1</v>
+      </c>
+      <c r="Q1978">
+        <v>0.625</v>
+      </c>
+      <c r="R1978" t="s">
+        <v>42</v>
+      </c>
+      <c r="S1978">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1979" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1979" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1979" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1979" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1979">
+        <v>90</v>
+      </c>
+      <c r="G1979">
+        <v>40</v>
+      </c>
+      <c r="H1979" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1979">
+        <v>0</v>
+      </c>
+      <c r="J1979">
+        <v>2</v>
+      </c>
+      <c r="K1979">
+        <v>28</v>
+      </c>
+      <c r="L1979">
+        <v>25</v>
+      </c>
+      <c r="M1979">
+        <v>3</v>
+      </c>
+      <c r="N1979">
+        <v>0.75</v>
+      </c>
+      <c r="O1979">
+        <v>0.5</v>
+      </c>
+      <c r="P1979">
+        <v>0.9375</v>
+      </c>
+      <c r="Q1979">
+        <v>0.625</v>
+      </c>
+      <c r="S1979">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1980" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1980" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1980" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1980" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1980">
+        <v>91</v>
+      </c>
+      <c r="G1980">
+        <v>41</v>
+      </c>
+      <c r="H1980" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1980">
+        <v>0</v>
+      </c>
+      <c r="K1980">
+        <v>28</v>
+      </c>
+      <c r="L1980">
+        <v>25</v>
+      </c>
+      <c r="M1980">
+        <v>3</v>
+      </c>
+      <c r="N1980">
+        <v>0.75</v>
+      </c>
+      <c r="O1980">
+        <v>0.25</v>
+      </c>
+      <c r="P1980">
+        <v>0.9375</v>
+      </c>
+      <c r="Q1980">
+        <v>0.5</v>
+      </c>
+      <c r="S1980">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1981" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1981" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1981" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1981" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1981">
+        <v>92</v>
+      </c>
+      <c r="G1981">
+        <v>41</v>
+      </c>
+      <c r="H1981" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1981">
+        <v>0</v>
+      </c>
+      <c r="J1981">
+        <v>0</v>
+      </c>
+      <c r="K1981">
+        <v>28</v>
+      </c>
+      <c r="L1981">
+        <v>25</v>
+      </c>
+      <c r="M1981">
+        <v>3</v>
+      </c>
+      <c r="N1981">
+        <v>0.5</v>
+      </c>
+      <c r="O1981">
+        <v>0.25</v>
+      </c>
+      <c r="P1981">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1981">
+        <v>0.5</v>
+      </c>
+      <c r="S1981">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1982" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1982" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1982" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1982" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1982">
+        <v>93</v>
+      </c>
+      <c r="G1982">
+        <v>41</v>
+      </c>
+      <c r="H1982" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1982">
+        <v>0</v>
+      </c>
+      <c r="K1982">
+        <v>28</v>
+      </c>
+      <c r="L1982">
+        <v>25</v>
+      </c>
+      <c r="M1982">
+        <v>3</v>
+      </c>
+      <c r="N1982">
+        <v>0.5</v>
+      </c>
+      <c r="O1982">
+        <v>0.25</v>
+      </c>
+      <c r="P1982">
+        <v>0.8125</v>
+      </c>
+      <c r="Q1982">
+        <v>0.4375</v>
+      </c>
+      <c r="S1982">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1983" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1983" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1983" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1983" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1983">
+        <v>94</v>
+      </c>
+      <c r="G1983">
+        <v>42</v>
+      </c>
+      <c r="H1983" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1983">
+        <v>1</v>
+      </c>
+      <c r="J1983">
+        <v>3</v>
+      </c>
+      <c r="K1983">
+        <v>29</v>
+      </c>
+      <c r="L1983">
+        <v>25</v>
+      </c>
+      <c r="M1983">
+        <v>4</v>
+      </c>
+      <c r="N1983">
+        <v>0.5</v>
+      </c>
+      <c r="O1983">
+        <v>0.25</v>
+      </c>
+      <c r="P1983">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1983">
+        <v>0.4375</v>
+      </c>
+      <c r="S1983">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A1984" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1984" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1984" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1984" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1984">
+        <v>95</v>
+      </c>
+      <c r="G1984">
+        <v>42</v>
+      </c>
+      <c r="H1984" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1984">
+        <v>0</v>
+      </c>
+      <c r="K1984">
+        <v>29</v>
+      </c>
+      <c r="L1984">
+        <v>25</v>
+      </c>
+      <c r="M1984">
+        <v>4</v>
+      </c>
+      <c r="N1984">
+        <v>0.5</v>
+      </c>
+      <c r="O1984">
+        <v>0</v>
+      </c>
+      <c r="P1984">
+        <v>0.6875</v>
+      </c>
+      <c r="Q1984">
+        <v>0.25</v>
+      </c>
+      <c r="S1984">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1985" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1985" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1985" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1985" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1985">
+        <v>96</v>
+      </c>
+      <c r="G1985">
+        <v>43</v>
+      </c>
+      <c r="H1985" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1985">
+        <v>0</v>
+      </c>
+      <c r="J1985">
+        <v>2</v>
+      </c>
+      <c r="K1985">
+        <v>29</v>
+      </c>
+      <c r="L1985">
+        <v>25</v>
+      </c>
+      <c r="M1985">
+        <v>4</v>
+      </c>
+      <c r="N1985">
+        <v>0.25</v>
+      </c>
+      <c r="O1985">
+        <v>0</v>
+      </c>
+      <c r="P1985">
+        <v>0.5</v>
+      </c>
+      <c r="Q1985">
+        <v>0.25</v>
+      </c>
+      <c r="S1985">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1986" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1986" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1986" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1986" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1986">
+        <v>97</v>
+      </c>
+      <c r="G1986">
+        <v>43</v>
+      </c>
+      <c r="H1986" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1986">
+        <v>1</v>
+      </c>
+      <c r="K1986">
+        <v>29</v>
+      </c>
+      <c r="L1986">
+        <v>26</v>
+      </c>
+      <c r="M1986">
+        <v>3</v>
+      </c>
+      <c r="N1986">
+        <v>0.25</v>
+      </c>
+      <c r="O1986">
+        <v>0.25</v>
+      </c>
+      <c r="P1986">
+        <v>0.5</v>
+      </c>
+      <c r="Q1986">
+        <v>0.1875</v>
+      </c>
+      <c r="S1986">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1987" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1987" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1987" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1987" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1987">
+        <v>98</v>
+      </c>
+      <c r="G1987">
+        <v>43</v>
+      </c>
+      <c r="H1987" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1987">
+        <v>0</v>
+      </c>
+      <c r="J1987">
+        <v>0</v>
+      </c>
+      <c r="K1987">
+        <v>29</v>
+      </c>
+      <c r="L1987">
+        <v>26</v>
+      </c>
+      <c r="M1987">
+        <v>3</v>
+      </c>
+      <c r="N1987">
+        <v>0.25</v>
+      </c>
+      <c r="O1987">
+        <v>0.25</v>
+      </c>
+      <c r="P1987">
+        <v>0.375</v>
+      </c>
+      <c r="Q1987">
+        <v>0.1875</v>
+      </c>
+      <c r="S1987">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1988" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1988" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1988" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1988" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1988">
+        <v>99</v>
+      </c>
+      <c r="G1988">
+        <v>44</v>
+      </c>
+      <c r="H1988" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1988">
+        <v>0</v>
+      </c>
+      <c r="K1988">
+        <v>29</v>
+      </c>
+      <c r="L1988">
+        <v>26</v>
+      </c>
+      <c r="M1988">
+        <v>3</v>
+      </c>
+      <c r="N1988">
+        <v>0.25</v>
+      </c>
+      <c r="O1988">
+        <v>0.25</v>
+      </c>
+      <c r="P1988">
+        <v>0.375</v>
+      </c>
+      <c r="Q1988">
+        <v>0.1875</v>
+      </c>
+      <c r="S1988">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1989" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1989" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1989" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1989" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1989">
+        <v>100</v>
+      </c>
+      <c r="G1989">
+        <v>44</v>
+      </c>
+      <c r="H1989" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1989">
+        <v>1</v>
+      </c>
+      <c r="J1989">
+        <v>24</v>
+      </c>
+      <c r="K1989">
+        <v>30</v>
+      </c>
+      <c r="L1989">
+        <v>26</v>
+      </c>
+      <c r="M1989">
+        <v>4</v>
+      </c>
+      <c r="N1989">
+        <v>0.5</v>
+      </c>
+      <c r="O1989">
+        <v>0.25</v>
+      </c>
+      <c r="P1989">
+        <v>0.375</v>
+      </c>
+      <c r="Q1989">
+        <v>0.1875</v>
+      </c>
+      <c r="S1989">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1990" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1990" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1990" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1990" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1990">
+        <v>101</v>
+      </c>
+      <c r="G1990">
+        <v>45</v>
+      </c>
+      <c r="H1990" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1990">
+        <v>0</v>
+      </c>
+      <c r="K1990">
+        <v>30</v>
+      </c>
+      <c r="L1990">
+        <v>26</v>
+      </c>
+      <c r="M1990">
+        <v>4</v>
+      </c>
+      <c r="N1990">
+        <v>0.5</v>
+      </c>
+      <c r="O1990">
+        <v>0.25</v>
+      </c>
+      <c r="P1990">
+        <v>0.375</v>
+      </c>
+      <c r="Q1990">
+        <v>0.1875</v>
+      </c>
+      <c r="S1990">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1991" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1991" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1991" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1991" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1991">
+        <v>102</v>
+      </c>
+      <c r="G1991">
+        <v>45</v>
+      </c>
+      <c r="H1991" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1991">
+        <v>0</v>
+      </c>
+      <c r="J1991">
+        <v>0</v>
+      </c>
+      <c r="K1991">
+        <v>30</v>
+      </c>
+      <c r="L1991">
+        <v>26</v>
+      </c>
+      <c r="M1991">
+        <v>4</v>
+      </c>
+      <c r="N1991">
+        <v>0.25</v>
+      </c>
+      <c r="O1991">
+        <v>0.25</v>
+      </c>
+      <c r="P1991">
+        <v>0.3125</v>
+      </c>
+      <c r="Q1991">
+        <v>0.1875</v>
+      </c>
+      <c r="S1991">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1992" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1992" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1992" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1992" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1992">
+        <v>103</v>
+      </c>
+      <c r="G1992">
+        <v>45</v>
+      </c>
+      <c r="H1992" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1992">
+        <v>1</v>
+      </c>
+      <c r="K1992">
+        <v>30</v>
+      </c>
+      <c r="L1992">
+        <v>27</v>
+      </c>
+      <c r="M1992">
+        <v>3</v>
+      </c>
+      <c r="N1992">
+        <v>0.25</v>
+      </c>
+      <c r="O1992">
+        <v>0.5</v>
+      </c>
+      <c r="P1992">
+        <v>0.3125</v>
+      </c>
+      <c r="Q1992">
+        <v>0.3125</v>
+      </c>
+      <c r="S1992">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1993" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1993" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1993" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1993" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1993">
+        <v>104</v>
+      </c>
+      <c r="G1993">
+        <v>45</v>
+      </c>
+      <c r="H1993" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1993">
+        <v>0</v>
+      </c>
+      <c r="J1993">
+        <v>0</v>
+      </c>
+      <c r="K1993">
+        <v>30</v>
+      </c>
+      <c r="L1993">
+        <v>27</v>
+      </c>
+      <c r="M1993">
+        <v>3</v>
+      </c>
+      <c r="N1993">
+        <v>0.25</v>
+      </c>
+      <c r="O1993">
+        <v>0.5</v>
+      </c>
+      <c r="P1993">
+        <v>0.3125</v>
+      </c>
+      <c r="Q1993">
+        <v>0.3125</v>
+      </c>
+      <c r="S1993">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1994" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1994" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1994" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1994" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1994">
+        <v>105</v>
+      </c>
+      <c r="G1994">
+        <v>46</v>
+      </c>
+      <c r="H1994" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1994">
+        <v>0</v>
+      </c>
+      <c r="K1994">
+        <v>30</v>
+      </c>
+      <c r="L1994">
+        <v>27</v>
+      </c>
+      <c r="M1994">
+        <v>3</v>
+      </c>
+      <c r="N1994">
+        <v>0.25</v>
+      </c>
+      <c r="O1994">
+        <v>0.25</v>
+      </c>
+      <c r="P1994">
+        <v>0.3125</v>
+      </c>
+      <c r="Q1994">
+        <v>0.3125</v>
+      </c>
+      <c r="S1994">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1995" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1995" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1995" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1995" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1995">
+        <v>106</v>
+      </c>
+      <c r="G1995">
+        <v>46</v>
+      </c>
+      <c r="H1995" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1995">
+        <v>0</v>
+      </c>
+      <c r="J1995">
+        <v>0</v>
+      </c>
+      <c r="K1995">
+        <v>30</v>
+      </c>
+      <c r="L1995">
+        <v>27</v>
+      </c>
+      <c r="M1995">
+        <v>3</v>
+      </c>
+      <c r="N1995">
+        <v>0.25</v>
+      </c>
+      <c r="O1995">
+        <v>0.25</v>
+      </c>
+      <c r="P1995">
+        <v>0.3125</v>
+      </c>
+      <c r="Q1995">
+        <v>0.3125</v>
+      </c>
+      <c r="S1995">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1996" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1996" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1996" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1996" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1996">
+        <v>107</v>
+      </c>
+      <c r="G1996">
+        <v>47</v>
+      </c>
+      <c r="H1996" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1996">
+        <v>1</v>
+      </c>
+      <c r="K1996">
+        <v>30</v>
+      </c>
+      <c r="L1996">
+        <v>28</v>
+      </c>
+      <c r="M1996">
+        <v>2</v>
+      </c>
+      <c r="N1996">
+        <v>0.25</v>
+      </c>
+      <c r="O1996">
+        <v>0.5</v>
+      </c>
+      <c r="P1996">
+        <v>0.3125</v>
+      </c>
+      <c r="Q1996">
+        <v>0.375</v>
+      </c>
+      <c r="S1996">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1997" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1997" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1997" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1997" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1997">
+        <v>108</v>
+      </c>
+      <c r="G1997">
+        <v>47</v>
+      </c>
+      <c r="H1997" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1997">
+        <v>0</v>
+      </c>
+      <c r="J1997">
+        <v>9</v>
+      </c>
+      <c r="K1997">
+        <v>30</v>
+      </c>
+      <c r="L1997">
+        <v>28</v>
+      </c>
+      <c r="M1997">
+        <v>2</v>
+      </c>
+      <c r="N1997">
+        <v>0</v>
+      </c>
+      <c r="O1997">
+        <v>0.5</v>
+      </c>
+      <c r="P1997">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1997">
+        <v>0.375</v>
+      </c>
+      <c r="S1997">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1998" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1998" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1998" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1998" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1998">
+        <v>109</v>
+      </c>
+      <c r="G1998">
+        <v>47</v>
+      </c>
+      <c r="H1998" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1998">
+        <v>1</v>
+      </c>
+      <c r="K1998">
+        <v>30</v>
+      </c>
+      <c r="L1998">
+        <v>29</v>
+      </c>
+      <c r="M1998">
+        <v>1</v>
+      </c>
+      <c r="N1998">
+        <v>0</v>
+      </c>
+      <c r="O1998">
+        <v>0.75</v>
+      </c>
+      <c r="P1998">
+        <v>0.1875</v>
+      </c>
+      <c r="Q1998">
+        <v>0.5</v>
+      </c>
+      <c r="S1998">
+        <v>-0.3125</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A1999" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1999" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1999" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1999" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1999">
+        <v>110</v>
+      </c>
+      <c r="G1999">
+        <v>48</v>
+      </c>
+      <c r="H1999" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1999">
+        <v>0</v>
+      </c>
+      <c r="J1999">
+        <v>0</v>
+      </c>
+      <c r="K1999">
+        <v>30</v>
+      </c>
+      <c r="L1999">
+        <v>29</v>
+      </c>
+      <c r="M1999">
+        <v>1</v>
+      </c>
+      <c r="N1999">
+        <v>0</v>
+      </c>
+      <c r="O1999">
+        <v>0.75</v>
+      </c>
+      <c r="P1999">
+        <v>0.125</v>
+      </c>
+      <c r="Q1999">
+        <v>0.5</v>
+      </c>
+      <c r="S1999">
+        <v>-0.375</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A2000" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2000" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2000" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2000" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2000">
+        <v>111</v>
+      </c>
+      <c r="G2000">
+        <v>49</v>
+      </c>
+      <c r="H2000" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2000">
+        <v>0</v>
+      </c>
+      <c r="K2000">
+        <v>30</v>
+      </c>
+      <c r="L2000">
+        <v>29</v>
+      </c>
+      <c r="M2000">
+        <v>1</v>
+      </c>
+      <c r="N2000">
+        <v>0</v>
+      </c>
+      <c r="O2000">
+        <v>0.5</v>
+      </c>
+      <c r="P2000">
+        <v>0.125</v>
+      </c>
+      <c r="Q2000">
+        <v>0.5</v>
+      </c>
+      <c r="S2000">
+        <v>-0.375</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2001" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2001" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2001" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2001" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2001">
+        <v>112</v>
+      </c>
+      <c r="G2001">
+        <v>49</v>
+      </c>
+      <c r="H2001" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2001">
+        <v>0</v>
+      </c>
+      <c r="J2001">
+        <v>0</v>
+      </c>
+      <c r="K2001">
+        <v>30</v>
+      </c>
+      <c r="L2001">
+        <v>29</v>
+      </c>
+      <c r="M2001">
+        <v>1</v>
+      </c>
+      <c r="N2001">
+        <v>0</v>
+      </c>
+      <c r="O2001">
+        <v>0.5</v>
+      </c>
+      <c r="P2001">
+        <v>6.25E-2</v>
+      </c>
+      <c r="Q2001">
+        <v>0.5</v>
+      </c>
+      <c r="S2001">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2002" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2002" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2002" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2002" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2002">
+        <v>113</v>
+      </c>
+      <c r="G2002">
+        <v>49</v>
+      </c>
+      <c r="H2002" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2002">
+        <v>0</v>
+      </c>
+      <c r="K2002">
+        <v>30</v>
+      </c>
+      <c r="L2002">
+        <v>29</v>
+      </c>
+      <c r="M2002">
+        <v>1</v>
+      </c>
+      <c r="N2002">
+        <v>0</v>
+      </c>
+      <c r="O2002">
+        <v>0.5</v>
+      </c>
+      <c r="P2002">
+        <v>6.25E-2</v>
+      </c>
+      <c r="Q2002">
+        <v>0.5625</v>
+      </c>
+      <c r="S2002">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2003" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2003" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2003" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2003" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2003">
+        <v>114</v>
+      </c>
+      <c r="G2003">
+        <v>50</v>
+      </c>
+      <c r="H2003" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2003">
+        <v>1</v>
+      </c>
+      <c r="J2003">
+        <v>2</v>
+      </c>
+      <c r="K2003">
+        <v>31</v>
+      </c>
+      <c r="L2003">
+        <v>29</v>
+      </c>
+      <c r="M2003">
+        <v>2</v>
+      </c>
+      <c r="N2003">
+        <v>0.25</v>
+      </c>
+      <c r="O2003">
+        <v>0.5</v>
+      </c>
+      <c r="P2003">
+        <v>6.25E-2</v>
+      </c>
+      <c r="Q2003">
+        <v>0.5625</v>
+      </c>
+      <c r="R2003" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2003">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2004" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2004" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2004" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2004" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2004">
+        <v>115</v>
+      </c>
+      <c r="G2004">
+        <v>51</v>
+      </c>
+      <c r="H2004" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2004">
+        <v>0</v>
+      </c>
+      <c r="K2004">
+        <v>31</v>
+      </c>
+      <c r="L2004">
+        <v>29</v>
+      </c>
+      <c r="M2004">
+        <v>2</v>
+      </c>
+      <c r="N2004">
+        <v>0.25</v>
+      </c>
+      <c r="O2004">
+        <v>0.25</v>
+      </c>
+      <c r="P2004">
+        <v>6.25E-2</v>
+      </c>
+      <c r="Q2004">
+        <v>0.5</v>
+      </c>
+      <c r="S2004">
+        <v>-0.4375</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2005" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2005" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2005" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2005" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2005">
+        <v>116</v>
+      </c>
+      <c r="G2005">
+        <v>51</v>
+      </c>
+      <c r="H2005" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2005">
+        <v>1</v>
+      </c>
+      <c r="J2005">
+        <v>25</v>
+      </c>
+      <c r="K2005">
+        <v>32</v>
+      </c>
+      <c r="L2005">
+        <v>29</v>
+      </c>
+      <c r="M2005">
+        <v>3</v>
+      </c>
+      <c r="N2005">
+        <v>0.5</v>
+      </c>
+      <c r="O2005">
+        <v>0.25</v>
+      </c>
+      <c r="P2005">
+        <v>0.1875</v>
+      </c>
+      <c r="Q2005">
+        <v>0.5</v>
+      </c>
+      <c r="S2005">
+        <v>-0.3125</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2006" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2006" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2006" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2006" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2006">
+        <v>117</v>
+      </c>
+      <c r="G2006">
+        <v>51</v>
+      </c>
+      <c r="H2006" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2006">
+        <v>1</v>
+      </c>
+      <c r="K2006">
+        <v>32</v>
+      </c>
+      <c r="L2006">
+        <v>30</v>
+      </c>
+      <c r="M2006">
+        <v>2</v>
+      </c>
+      <c r="N2006">
+        <v>0.5</v>
+      </c>
+      <c r="O2006">
+        <v>0.25</v>
+      </c>
+      <c r="P2006">
+        <v>0.1875</v>
+      </c>
+      <c r="Q2006">
+        <v>0.375</v>
+      </c>
+      <c r="S2006">
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2007" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2007" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2007" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2007" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2007">
+        <v>118</v>
+      </c>
+      <c r="G2007">
+        <v>51</v>
+      </c>
+      <c r="H2007" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2007">
+        <v>0</v>
+      </c>
+      <c r="J2007">
+        <v>0</v>
+      </c>
+      <c r="K2007">
+        <v>32</v>
+      </c>
+      <c r="L2007">
+        <v>30</v>
+      </c>
+      <c r="M2007">
+        <v>2</v>
+      </c>
+      <c r="N2007">
+        <v>0.5</v>
+      </c>
+      <c r="O2007">
+        <v>0.25</v>
+      </c>
+      <c r="P2007">
+        <v>0.3125</v>
+      </c>
+      <c r="Q2007">
+        <v>0.375</v>
+      </c>
+      <c r="S2007">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2008" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2008" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2008" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2008" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2008" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2008">
+        <v>119</v>
+      </c>
+      <c r="G2008">
+        <v>52</v>
+      </c>
+      <c r="H2008" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2008">
+        <v>1</v>
+      </c>
+      <c r="K2008">
+        <v>32</v>
+      </c>
+      <c r="L2008">
+        <v>31</v>
+      </c>
+      <c r="M2008">
+        <v>1</v>
+      </c>
+      <c r="N2008">
+        <v>0.5</v>
+      </c>
+      <c r="O2008">
+        <v>0.5</v>
+      </c>
+      <c r="P2008">
+        <v>0.3125</v>
+      </c>
+      <c r="Q2008">
+        <v>0.375</v>
+      </c>
+      <c r="S2008">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2009" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2009" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2009" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2009" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2009" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2009">
+        <v>120</v>
+      </c>
+      <c r="G2009">
+        <v>52</v>
+      </c>
+      <c r="H2009" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2009">
+        <v>1</v>
+      </c>
+      <c r="J2009">
+        <v>9</v>
+      </c>
+      <c r="K2009">
+        <v>33</v>
+      </c>
+      <c r="L2009">
+        <v>31</v>
+      </c>
+      <c r="M2009">
+        <v>2</v>
+      </c>
+      <c r="N2009">
+        <v>0.75</v>
+      </c>
+      <c r="O2009">
+        <v>0.5</v>
+      </c>
+      <c r="P2009">
+        <v>0.5</v>
+      </c>
+      <c r="Q2009">
+        <v>0.375</v>
+      </c>
+      <c r="S2009">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2010" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2010" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2010" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2010" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2010" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2010">
+        <v>121</v>
+      </c>
+      <c r="G2010">
+        <v>53</v>
+      </c>
+      <c r="H2010" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2010">
+        <v>1</v>
+      </c>
+      <c r="K2010">
+        <v>33</v>
+      </c>
+      <c r="L2010">
+        <v>32</v>
+      </c>
+      <c r="M2010">
+        <v>1</v>
+      </c>
+      <c r="N2010">
+        <v>0.75</v>
+      </c>
+      <c r="O2010">
+        <v>0.75</v>
+      </c>
+      <c r="P2010">
+        <v>0.5</v>
+      </c>
+      <c r="Q2010">
+        <v>0.4375</v>
+      </c>
+      <c r="S2010">
+        <v>6.25E-2</v>
+      </c>
+      <c r="U2010" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2011" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2011" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2011" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2011" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2011" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2011">
+        <v>122</v>
+      </c>
+      <c r="G2011">
+        <v>53</v>
+      </c>
+      <c r="H2011" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2011">
+        <v>1</v>
+      </c>
+      <c r="J2011">
+        <v>9</v>
+      </c>
+      <c r="K2011">
+        <v>34</v>
+      </c>
+      <c r="L2011">
+        <v>32</v>
+      </c>
+      <c r="M2011">
+        <v>2</v>
+      </c>
+      <c r="N2011">
+        <v>0.75</v>
+      </c>
+      <c r="O2011">
+        <v>0.75</v>
+      </c>
+      <c r="P2011">
+        <v>0.625</v>
+      </c>
+      <c r="Q2011">
+        <v>0.4375</v>
+      </c>
+      <c r="S2011">
+        <v>0.1875</v>
+      </c>
+      <c r="U2011" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2012" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2012" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2012" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2012" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2012" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2012">
+        <v>123</v>
+      </c>
+      <c r="G2012">
+        <v>54</v>
+      </c>
+      <c r="H2012" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2012">
+        <v>1</v>
+      </c>
+      <c r="K2012">
+        <v>34</v>
+      </c>
+      <c r="L2012">
+        <v>33</v>
+      </c>
+      <c r="M2012">
+        <v>1</v>
+      </c>
+      <c r="N2012">
+        <v>0.75</v>
+      </c>
+      <c r="O2012">
+        <v>1</v>
+      </c>
+      <c r="P2012">
+        <v>0.625</v>
+      </c>
+      <c r="Q2012">
+        <v>0.625</v>
+      </c>
+      <c r="S2012">
+        <v>0</v>
+      </c>
+      <c r="U2012" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2013" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2013" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2013" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2013" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2013" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2013">
+        <v>124</v>
+      </c>
+      <c r="G2013">
+        <v>54</v>
+      </c>
+      <c r="H2013" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2013">
+        <v>1</v>
+      </c>
+      <c r="J2013">
+        <v>2</v>
+      </c>
+      <c r="K2013">
+        <v>35</v>
+      </c>
+      <c r="L2013">
+        <v>33</v>
+      </c>
+      <c r="M2013">
+        <v>2</v>
+      </c>
+      <c r="N2013">
+        <v>0.75</v>
+      </c>
+      <c r="O2013">
+        <v>1</v>
+      </c>
+      <c r="P2013">
+        <v>0.6875</v>
+      </c>
+      <c r="Q2013">
+        <v>0.625</v>
+      </c>
+      <c r="S2013">
+        <v>6.25E-2</v>
+      </c>
+      <c r="U2013" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2014" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2014" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2014" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2014" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2014" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2014">
+        <v>125</v>
+      </c>
+      <c r="G2014">
+        <v>55</v>
+      </c>
+      <c r="H2014" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2014">
+        <v>0</v>
+      </c>
+      <c r="K2014">
+        <v>35</v>
+      </c>
+      <c r="L2014">
+        <v>33</v>
+      </c>
+      <c r="M2014">
+        <v>2</v>
+      </c>
+      <c r="N2014">
+        <v>0.75</v>
+      </c>
+      <c r="O2014">
+        <v>0.75</v>
+      </c>
+      <c r="P2014">
+        <v>0.6875</v>
+      </c>
+      <c r="Q2014">
+        <v>0.75</v>
+      </c>
+      <c r="R2014" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2014">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2015" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2015" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2015" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2015" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2015" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2015">
+        <v>126</v>
+      </c>
+      <c r="G2015">
+        <v>56</v>
+      </c>
+      <c r="H2015" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2015">
+        <v>1</v>
+      </c>
+      <c r="J2015">
+        <v>4</v>
+      </c>
+      <c r="K2015">
+        <v>36</v>
+      </c>
+      <c r="L2015">
+        <v>33</v>
+      </c>
+      <c r="M2015">
+        <v>3</v>
+      </c>
+      <c r="N2015">
+        <v>1</v>
+      </c>
+      <c r="O2015">
+        <v>0.75</v>
+      </c>
+      <c r="P2015">
+        <v>0.8125</v>
+      </c>
+      <c r="Q2015">
+        <v>0.75</v>
+      </c>
+      <c r="S2015">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2016" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2016" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2016" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2016" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2016" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2016">
+        <v>127</v>
+      </c>
+      <c r="G2016">
+        <v>56</v>
+      </c>
+      <c r="H2016" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2016">
+        <v>1</v>
+      </c>
+      <c r="K2016">
+        <v>36</v>
+      </c>
+      <c r="L2016">
+        <v>34</v>
+      </c>
+      <c r="M2016">
+        <v>2</v>
+      </c>
+      <c r="N2016">
+        <v>1</v>
+      </c>
+      <c r="O2016">
+        <v>0.75</v>
+      </c>
+      <c r="P2016">
+        <v>0.8125</v>
+      </c>
+      <c r="Q2016">
+        <v>0.8125</v>
+      </c>
+      <c r="S2016">
+        <v>0</v>
+      </c>
+      <c r="T2016" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2017" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2017" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2017" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2017" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2017" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2017">
+        <v>128</v>
+      </c>
+      <c r="G2017">
+        <v>57</v>
+      </c>
+      <c r="H2017" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2017">
+        <v>0</v>
+      </c>
+      <c r="J2017">
+        <v>2</v>
+      </c>
+      <c r="K2017">
+        <v>36</v>
+      </c>
+      <c r="L2017">
+        <v>34</v>
+      </c>
+      <c r="M2017">
+        <v>2</v>
+      </c>
+      <c r="N2017">
+        <v>0.75</v>
+      </c>
+      <c r="O2017">
+        <v>0.75</v>
+      </c>
+      <c r="P2017">
+        <v>0.8125</v>
+      </c>
+      <c r="Q2017">
+        <v>0.8125</v>
+      </c>
+      <c r="S2017">
+        <v>0</v>
+      </c>
+      <c r="T2017" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2018" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2018" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2018" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2018" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2018" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2018">
+        <v>129</v>
+      </c>
+      <c r="G2018">
+        <v>58</v>
+      </c>
+      <c r="H2018" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2018">
+        <v>1</v>
+      </c>
+      <c r="K2018">
+        <v>36</v>
+      </c>
+      <c r="L2018">
+        <v>35</v>
+      </c>
+      <c r="M2018">
+        <v>1</v>
+      </c>
+      <c r="N2018">
+        <v>0.75</v>
+      </c>
+      <c r="O2018">
+        <v>0.75</v>
+      </c>
+      <c r="P2018">
+        <v>0.8125</v>
+      </c>
+      <c r="Q2018">
+        <v>0.8125</v>
+      </c>
+      <c r="S2018">
+        <v>0</v>
+      </c>
+      <c r="T2018" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2019" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2019" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2019" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2019" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2019">
+        <v>130</v>
+      </c>
+      <c r="G2019">
+        <v>59</v>
+      </c>
+      <c r="H2019" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2019">
+        <v>1</v>
+      </c>
+      <c r="J2019">
+        <v>2</v>
+      </c>
+      <c r="K2019">
+        <v>37</v>
+      </c>
+      <c r="L2019">
+        <v>35</v>
+      </c>
+      <c r="M2019">
+        <v>2</v>
+      </c>
+      <c r="N2019">
+        <v>0.75</v>
+      </c>
+      <c r="O2019">
+        <v>0.75</v>
+      </c>
+      <c r="P2019">
+        <v>0.8125</v>
+      </c>
+      <c r="Q2019">
+        <v>0.8125</v>
+      </c>
+      <c r="S2019">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2020" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2020" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2020" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2020" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2020" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2020">
+        <v>131</v>
+      </c>
+      <c r="G2020">
+        <v>59</v>
+      </c>
+      <c r="H2020" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2020">
+        <v>0</v>
+      </c>
+      <c r="K2020">
+        <v>37</v>
+      </c>
+      <c r="L2020">
+        <v>35</v>
+      </c>
+      <c r="M2020">
+        <v>2</v>
+      </c>
+      <c r="N2020">
+        <v>0.75</v>
+      </c>
+      <c r="O2020">
+        <v>0.5</v>
+      </c>
+      <c r="P2020">
+        <v>0.8125</v>
+      </c>
+      <c r="Q2020">
+        <v>0.6875</v>
+      </c>
+      <c r="S2020">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2021" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2021" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2021" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2021" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2021" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2021">
+        <v>132</v>
+      </c>
+      <c r="G2021">
+        <v>59</v>
+      </c>
+      <c r="H2021" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2021">
+        <v>0</v>
+      </c>
+      <c r="J2021">
+        <v>0</v>
+      </c>
+      <c r="K2021">
+        <v>37</v>
+      </c>
+      <c r="L2021">
+        <v>35</v>
+      </c>
+      <c r="M2021">
+        <v>2</v>
+      </c>
+      <c r="N2021">
+        <v>0.5</v>
+      </c>
+      <c r="O2021">
+        <v>0.5</v>
+      </c>
+      <c r="P2021">
+        <v>0.75</v>
+      </c>
+      <c r="Q2021">
+        <v>0.6875</v>
+      </c>
+      <c r="S2021">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2022" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2022" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2022" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2022" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2022" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2022">
+        <v>133</v>
+      </c>
+      <c r="G2022">
+        <v>60</v>
+      </c>
+      <c r="H2022" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2022">
+        <v>0</v>
+      </c>
+      <c r="K2022">
+        <v>37</v>
+      </c>
+      <c r="L2022">
+        <v>35</v>
+      </c>
+      <c r="M2022">
+        <v>2</v>
+      </c>
+      <c r="N2022">
+        <v>0.5</v>
+      </c>
+      <c r="O2022">
+        <v>0.5</v>
+      </c>
+      <c r="P2022">
+        <v>0.75</v>
+      </c>
+      <c r="Q2022">
+        <v>0.625</v>
+      </c>
+      <c r="S2022">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2023" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2023" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2023" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2023" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2023" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2023">
+        <v>134</v>
+      </c>
+      <c r="G2023">
+        <v>60</v>
+      </c>
+      <c r="H2023" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2023">
+        <v>0</v>
+      </c>
+      <c r="J2023">
+        <v>0</v>
+      </c>
+      <c r="K2023">
+        <v>37</v>
+      </c>
+      <c r="L2023">
+        <v>35</v>
+      </c>
+      <c r="M2023">
+        <v>2</v>
+      </c>
+      <c r="N2023">
+        <v>0.25</v>
+      </c>
+      <c r="O2023">
+        <v>0.5</v>
+      </c>
+      <c r="P2023">
+        <v>0.5625</v>
+      </c>
+      <c r="Q2023">
+        <v>0.625</v>
+      </c>
+      <c r="R2023" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2023">
+        <v>-6.25E-2</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A2024" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2024" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2024" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2024" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2024">
+        <v>135</v>
+      </c>
+      <c r="G2024">
+        <v>60</v>
+      </c>
+      <c r="H2024" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2024">
+        <v>0</v>
+      </c>
+      <c r="K2024">
+        <v>37</v>
+      </c>
+      <c r="L2024">
+        <v>35</v>
+      </c>
+      <c r="M2024">
+        <v>2</v>
+      </c>
+      <c r="N2024">
+        <v>0.25</v>
+      </c>
+      <c r="O2024">
+        <v>0.25</v>
+      </c>
+      <c r="P2024">
+        <v>0.5625</v>
+      </c>
+      <c r="Q2024">
+        <v>0.5</v>
+      </c>
+      <c r="S2024">
+        <v>6.25E-2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
